--- a/files/vol_marks.xlsx
+++ b/files/vol_marks.xlsx
@@ -55245,156 +55245,155 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultColWidth="8.82421875" defaultRowHeight="12.75" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>9</v>
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>PAIRS</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>TENORS</t>
+        </is>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>14</v>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>1w</t>
+        </is>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>18</v>
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>2w</t>
+        </is>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>19</v>
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>USDCNY</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>3w</t>
+        </is>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>20</v>
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>21</v>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2m</t>
+        </is>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>22</v>
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>23</v>
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I9" s="2" t="s">
-        <v>24</v>
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>9m</t>
+        </is>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I10" s="2" t="s">
-        <v>25</v>
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>AUDJPY</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>1y</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>GBPNZD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>EURCNH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>GBPCNH</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/files/vol_marks.xlsx
+++ b/files/vol_marks.xlsx
@@ -27,8 +27,9 @@
     <sheet name="USDCNH" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="USDCNY" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="PARAMS" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Sales Margin" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="EVENTS" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Vega Weights" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="BANDS" sheetId="24" state="visible" r:id="rId24"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -36,7 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="&quot; &quot;* #,##0.000&quot; &quot;;&quot; &quot;* (#,##0.000);&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -45,9 +46,10 @@
     <numFmt numFmtId="169" formatCode="&quot; &quot;* #,##0.00000&quot; &quot;;&quot; &quot;* (#,##0.00000);&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
     <numFmt numFmtId="170" formatCode="0.000%"/>
     <numFmt numFmtId="171" formatCode="&quot; &quot;* #,##0.00&quot; &quot;;&quot; &quot;* (#,##0.00);&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
-    <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="173" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <name val="Arial"/>
       <color indexed="8"/>
@@ -99,14 +101,8 @@
       <color indexed="8"/>
       <sz val="11"/>
     </font>
-    <font>
-      <name val="Arial"/>
-      <charset val="1"/>
-      <family val="2"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -127,7 +123,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="13"/>
+        <fgColor indexed="12"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -161,12 +157,6 @@
         <bgColor auto="1"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD0CECE"/>
-        <bgColor rgb="FFD9D9D9"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="17">
     <border>
@@ -178,11 +168,11 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </left>
       <right/>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -191,7 +181,7 @@
       <left/>
       <right/>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -199,17 +189,17 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </left>
       <right/>
       <top/>
@@ -226,7 +216,7 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </right>
       <top/>
       <bottom/>
@@ -234,12 +224,23 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </left>
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
@@ -248,100 +249,89 @@
       <right/>
       <top/>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right style="thin">
+        <color indexed="13"/>
+      </right>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="13"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color indexed="13"/>
+      </top>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="12"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top style="thin">
-        <color indexed="12"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="12"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
-      </left>
-      <right style="thin">
-        <color indexed="12"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="12"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </left>
       <right style="thin">
         <color indexed="8"/>
       </right>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
@@ -350,13 +340,13 @@
         <color indexed="8"/>
       </left>
       <right style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </right>
       <top style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </top>
       <bottom style="thin">
-        <color indexed="12"/>
+        <color indexed="13"/>
       </bottom>
       <diagonal/>
     </border>
@@ -366,7 +356,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -388,28 +378,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="2" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -427,20 +417,20 @@
     <xf numFmtId="49" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
@@ -478,12 +468,12 @@
     <xf numFmtId="1" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="1" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -493,6 +483,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -505,81 +525,166 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="9" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="171" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="7" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="9" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -598,106 +703,10 @@
     <xf numFmtId="171" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="167" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="169" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="170" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="171" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="172" fontId="0" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -717,8 +726,8 @@
       <rgbColor rgb="ff5e88b1"/>
       <rgbColor rgb="ffeef3f4"/>
       <rgbColor rgb="ff0000ff"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ff6a8759"/>
       <rgbColor rgb="ffd0cece"/>
       <rgbColor rgb="ffd9d9d9"/>
@@ -1761,32 +1770,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10" defaultRowHeight="13" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="2" customWidth="1" style="90" min="1" max="1"/>
-    <col width="33.6719" customWidth="1" style="90" min="2" max="2"/>
-    <col width="33.6719" customWidth="1" style="90" min="3" max="3"/>
-    <col width="33.6719" customWidth="1" style="90" min="4" max="4"/>
-    <col width="10" customWidth="1" style="90" min="5" max="5"/>
-    <col width="10" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="2" customWidth="1" style="99" min="1" max="1"/>
+    <col width="33.6719" customWidth="1" style="99" min="2" max="2"/>
+    <col width="33.6719" customWidth="1" style="99" min="3" max="3"/>
+    <col width="33.6719" customWidth="1" style="99" min="4" max="4"/>
+    <col width="10" customWidth="1" style="99" min="5" max="5"/>
+    <col width="10" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="7" t="n"/>
       <c r="B1" s="8" t="n"/>
       <c r="C1" s="8" t="n"/>
       <c r="D1" s="8" t="n"/>
       <c r="E1" s="9" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="10" t="n"/>
       <c r="B2" s="11" t="n"/>
       <c r="C2" s="11" t="n"/>
       <c r="D2" s="11" t="n"/>
       <c r="E2" s="12" t="n"/>
     </row>
-    <row r="3" ht="0.05" customHeight="1" s="93">
+    <row r="3" ht="0.05" customHeight="1" s="102">
       <c r="A3" s="10" t="n"/>
       <c r="B3" s="13" t="inlineStr">
         <is>
@@ -1795,21 +1804,21 @@
       </c>
       <c r="E3" s="12" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="10" t="n"/>
       <c r="B4" s="11" t="n"/>
       <c r="C4" s="11" t="n"/>
       <c r="D4" s="11" t="n"/>
       <c r="E4" s="12" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="10" t="n"/>
       <c r="B5" s="11" t="n"/>
       <c r="C5" s="11" t="n"/>
       <c r="D5" s="11" t="n"/>
       <c r="E5" s="12" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="11" t="n"/>
       <c r="C6" s="11" t="n"/>
@@ -1835,7 +1844,7 @@
       </c>
       <c r="E7" s="12" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="10" t="n"/>
       <c r="B8" s="11" t="n"/>
       <c r="C8" s="11" t="n"/>
@@ -1868,7 +1877,7 @@
       </c>
       <c r="E10" s="12" t="n"/>
     </row>
-    <row r="11" ht="13" customHeight="1" s="93">
+    <row r="11" ht="13" customHeight="1" s="102">
       <c r="A11" s="10" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -1879,7 +1888,7 @@
       <c r="D11" s="3" t="n"/>
       <c r="E11" s="12" t="n"/>
     </row>
-    <row r="12" ht="13" customHeight="1" s="93">
+    <row r="12" ht="13" customHeight="1" s="102">
       <c r="A12" s="10" t="n"/>
       <c r="B12" s="4" t="n"/>
       <c r="C12" s="4" t="inlineStr">
@@ -1894,7 +1903,7 @@
       </c>
       <c r="E12" s="12" t="n"/>
     </row>
-    <row r="13" ht="13" customHeight="1" s="93">
+    <row r="13" ht="13" customHeight="1" s="102">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -1905,7 +1914,7 @@
       <c r="D13" s="3" t="n"/>
       <c r="E13" s="12" t="n"/>
     </row>
-    <row r="14" ht="13" customHeight="1" s="93">
+    <row r="14" ht="13" customHeight="1" s="102">
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="4" t="n"/>
       <c r="C14" s="4" t="inlineStr">
@@ -1920,7 +1929,7 @@
       </c>
       <c r="E14" s="12" t="n"/>
     </row>
-    <row r="15" ht="13" customHeight="1" s="93">
+    <row r="15" ht="13" customHeight="1" s="102">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
@@ -1931,7 +1940,7 @@
       <c r="D15" s="3" t="n"/>
       <c r="E15" s="12" t="n"/>
     </row>
-    <row r="16" ht="13" customHeight="1" s="93">
+    <row r="16" ht="13" customHeight="1" s="102">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="4" t="n"/>
       <c r="C16" s="4" t="inlineStr">
@@ -1946,7 +1955,7 @@
       </c>
       <c r="E16" s="12" t="n"/>
     </row>
-    <row r="17" ht="13" customHeight="1" s="93">
+    <row r="17" ht="13" customHeight="1" s="102">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
@@ -1957,7 +1966,7 @@
       <c r="D17" s="3" t="n"/>
       <c r="E17" s="12" t="n"/>
     </row>
-    <row r="18" ht="13" customHeight="1" s="93">
+    <row r="18" ht="13" customHeight="1" s="102">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="4" t="n"/>
       <c r="C18" s="4" t="inlineStr">
@@ -1972,7 +1981,7 @@
       </c>
       <c r="E18" s="12" t="n"/>
     </row>
-    <row r="19" ht="13" customHeight="1" s="93">
+    <row r="19" ht="13" customHeight="1" s="102">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
@@ -1983,7 +1992,7 @@
       <c r="D19" s="3" t="n"/>
       <c r="E19" s="12" t="n"/>
     </row>
-    <row r="20" ht="13" customHeight="1" s="93">
+    <row r="20" ht="13" customHeight="1" s="102">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="4" t="n"/>
       <c r="C20" s="4" t="inlineStr">
@@ -1998,18 +2007,18 @@
       </c>
       <c r="E20" s="12" t="n"/>
     </row>
-    <row r="21" ht="13" customHeight="1" s="93">
+    <row r="21" ht="13" customHeight="1" s="102">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="12" t="n"/>
     </row>
-    <row r="22" ht="13" customHeight="1" s="93">
+    <row r="22" ht="13" customHeight="1" s="102">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="4" t="n"/>
       <c r="C22" s="4" t="inlineStr">
@@ -2019,23 +2028,23 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>USDHKD</t>
+          <t>EURGBP</t>
         </is>
       </c>
       <c r="E22" s="12" t="n"/>
     </row>
-    <row r="23" ht="13" customHeight="1" s="93">
+    <row r="23" ht="13" customHeight="1" s="102">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>GBPCNH</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="C23" s="3" t="n"/>
       <c r="D23" s="3" t="n"/>
       <c r="E23" s="12" t="n"/>
     </row>
-    <row r="24" ht="13" customHeight="1" s="93">
+    <row r="24" ht="13" customHeight="1" s="102">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="4" t="n"/>
       <c r="C24" s="4" t="inlineStr">
@@ -2045,23 +2054,23 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>GBPCNH</t>
+          <t>USDHKD</t>
         </is>
       </c>
       <c r="E24" s="12" t="n"/>
     </row>
-    <row r="25" ht="13" customHeight="1" s="93">
+    <row r="25" ht="13" customHeight="1" s="102">
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>AUDCNH</t>
+          <t>GBPCNH</t>
         </is>
       </c>
       <c r="C25" s="3" t="n"/>
       <c r="D25" s="3" t="n"/>
       <c r="E25" s="12" t="n"/>
     </row>
-    <row r="26" ht="13" customHeight="1" s="93">
+    <row r="26" ht="13" customHeight="1" s="102">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="4" t="n"/>
       <c r="C26" s="4" t="inlineStr">
@@ -2071,23 +2080,23 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>AUDCNH</t>
+          <t>GBPCNH</t>
         </is>
       </c>
       <c r="E26" s="12" t="n"/>
     </row>
-    <row r="27" ht="13" customHeight="1" s="93">
+    <row r="27" ht="13" customHeight="1" s="102">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>NZDCNH</t>
+          <t>AUDCNH</t>
         </is>
       </c>
       <c r="C27" s="3" t="n"/>
       <c r="D27" s="3" t="n"/>
       <c r="E27" s="12" t="n"/>
     </row>
-    <row r="28" ht="13" customHeight="1" s="93">
+    <row r="28" ht="13" customHeight="1" s="102">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="4" t="n"/>
       <c r="C28" s="4" t="inlineStr">
@@ -2097,23 +2106,23 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>NZDCNH</t>
+          <t>AUDCNH</t>
         </is>
       </c>
       <c r="E28" s="12" t="n"/>
     </row>
-    <row r="29" ht="13" customHeight="1" s="93">
+    <row r="29" ht="13" customHeight="1" s="102">
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>CNHHKD</t>
+          <t>NZDCNH</t>
         </is>
       </c>
       <c r="C29" s="3" t="n"/>
       <c r="D29" s="3" t="n"/>
       <c r="E29" s="12" t="n"/>
     </row>
-    <row r="30" ht="13" customHeight="1" s="93">
+    <row r="30" ht="13" customHeight="1" s="102">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="4" t="n"/>
       <c r="C30" s="4" t="inlineStr">
@@ -2123,23 +2132,23 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>CNHHKD</t>
+          <t>NZDCNH</t>
         </is>
       </c>
       <c r="E30" s="12" t="n"/>
     </row>
-    <row r="31" ht="13" customHeight="1" s="93">
+    <row r="31" ht="13" customHeight="1" s="102">
       <c r="A31" s="10" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>EURCNH</t>
+          <t>CNHHKD</t>
         </is>
       </c>
       <c r="C31" s="3" t="n"/>
       <c r="D31" s="3" t="n"/>
       <c r="E31" s="12" t="n"/>
     </row>
-    <row r="32" ht="13" customHeight="1" s="93">
+    <row r="32" ht="13" customHeight="1" s="102">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="4" t="n"/>
       <c r="C32" s="4" t="inlineStr">
@@ -2149,23 +2158,23 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>EURCNH</t>
+          <t>CNHHKD</t>
         </is>
       </c>
       <c r="E32" s="12" t="n"/>
     </row>
-    <row r="33" ht="13" customHeight="1" s="93">
+    <row r="33" ht="13" customHeight="1" s="102">
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURCNH</t>
         </is>
       </c>
       <c r="C33" s="3" t="n"/>
       <c r="D33" s="3" t="n"/>
       <c r="E33" s="12" t="n"/>
     </row>
-    <row r="34" ht="13" customHeight="1" s="93">
+    <row r="34" ht="13" customHeight="1" s="102">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="4" t="n"/>
       <c r="C34" s="4" t="inlineStr">
@@ -2175,23 +2184,23 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>AUDJPY</t>
+          <t>EURCNH</t>
         </is>
       </c>
       <c r="E34" s="12" t="n"/>
     </row>
-    <row r="35" ht="13" customHeight="1" s="93">
+    <row r="35" ht="13" customHeight="1" s="102">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="C35" s="3" t="n"/>
       <c r="D35" s="3" t="n"/>
       <c r="E35" s="12" t="n"/>
     </row>
-    <row r="36" ht="13" customHeight="1" s="93">
+    <row r="36" ht="13" customHeight="1" s="102">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="4" t="n"/>
       <c r="C36" s="4" t="inlineStr">
@@ -2201,23 +2210,23 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>EURJPY</t>
+          <t>AUDJPY</t>
         </is>
       </c>
       <c r="E36" s="12" t="n"/>
     </row>
-    <row r="37" ht="13" customHeight="1" s="93">
+    <row r="37" ht="13" customHeight="1" s="102">
       <c r="A37" s="10" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="C37" s="3" t="n"/>
       <c r="D37" s="3" t="n"/>
       <c r="E37" s="12" t="n"/>
     </row>
-    <row r="38" ht="13" customHeight="1" s="93">
+    <row r="38" ht="13" customHeight="1" s="102">
       <c r="A38" s="10" t="n"/>
       <c r="B38" s="4" t="n"/>
       <c r="C38" s="4" t="inlineStr">
@@ -2227,23 +2236,23 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>EURUSD</t>
+          <t>EURJPY</t>
         </is>
       </c>
       <c r="E38" s="12" t="n"/>
     </row>
-    <row r="39" ht="13" customHeight="1" s="93">
+    <row r="39" ht="13" customHeight="1" s="102">
       <c r="A39" s="10" t="n"/>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="C39" s="3" t="n"/>
       <c r="D39" s="3" t="n"/>
       <c r="E39" s="12" t="n"/>
     </row>
-    <row r="40" ht="13" customHeight="1" s="93">
+    <row r="40" ht="13" customHeight="1" s="102">
       <c r="A40" s="10" t="n"/>
       <c r="B40" s="4" t="n"/>
       <c r="C40" s="4" t="inlineStr">
@@ -2253,23 +2262,23 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>AUDUSD</t>
+          <t>EURUSD</t>
         </is>
       </c>
       <c r="E40" s="12" t="n"/>
     </row>
-    <row r="41" ht="13" customHeight="1" s="93">
+    <row r="41" ht="13" customHeight="1" s="102">
       <c r="A41" s="10" t="n"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="C41" s="3" t="n"/>
       <c r="D41" s="3" t="n"/>
       <c r="E41" s="12" t="n"/>
     </row>
-    <row r="42" ht="13" customHeight="1" s="93">
+    <row r="42" ht="13" customHeight="1" s="102">
       <c r="A42" s="10" t="n"/>
       <c r="B42" s="4" t="n"/>
       <c r="C42" s="4" t="inlineStr">
@@ -2279,23 +2288,23 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>USDJPY</t>
+          <t>AUDUSD</t>
         </is>
       </c>
       <c r="E42" s="12" t="n"/>
     </row>
-    <row r="43" ht="13" customHeight="1" s="93">
+    <row r="43" ht="13" customHeight="1" s="102">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="C43" s="3" t="n"/>
       <c r="D43" s="3" t="n"/>
       <c r="E43" s="12" t="n"/>
     </row>
-    <row r="44" ht="13" customHeight="1" s="93">
+    <row r="44" ht="13" customHeight="1" s="102">
       <c r="A44" s="10" t="n"/>
       <c r="B44" s="4" t="n"/>
       <c r="C44" s="4" t="inlineStr">
@@ -2305,23 +2314,23 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>USDJPY</t>
         </is>
       </c>
       <c r="E44" s="12" t="n"/>
     </row>
-    <row r="45" ht="13" customHeight="1" s="93">
+    <row r="45" ht="13" customHeight="1" s="102">
       <c r="A45" s="10" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>USDCNY</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="C45" s="3" t="n"/>
       <c r="D45" s="3" t="n"/>
       <c r="E45" s="12" t="n"/>
     </row>
-    <row r="46" ht="13" customHeight="1" s="93">
+    <row r="46" ht="13" customHeight="1" s="102">
       <c r="A46" s="10" t="n"/>
       <c r="B46" s="4" t="n"/>
       <c r="C46" s="4" t="inlineStr">
@@ -2331,23 +2340,23 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>USDCNY</t>
+          <t>USDCNH</t>
         </is>
       </c>
       <c r="E46" s="12" t="n"/>
     </row>
-    <row r="47" ht="13" customHeight="1" s="93">
+    <row r="47" ht="13" customHeight="1" s="102">
       <c r="A47" s="10" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PARAMS</t>
+          <t>USDCNY</t>
         </is>
       </c>
       <c r="C47" s="3" t="n"/>
       <c r="D47" s="3" t="n"/>
       <c r="E47" s="12" t="n"/>
     </row>
-    <row r="48" ht="13" customHeight="1" s="93">
+    <row r="48" ht="13" customHeight="1" s="102">
       <c r="A48" s="10" t="n"/>
       <c r="B48" s="4" t="n"/>
       <c r="C48" s="4" t="inlineStr">
@@ -2357,23 +2366,23 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>PARAMS</t>
+          <t>USDCNY</t>
         </is>
       </c>
       <c r="E48" s="12" t="n"/>
     </row>
-    <row r="49" ht="13" customHeight="1" s="93">
+    <row r="49" ht="13" customHeight="1" s="102">
       <c r="A49" s="10" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Sales Margin</t>
+          <t>PARAMS</t>
         </is>
       </c>
       <c r="C49" s="3" t="n"/>
       <c r="D49" s="3" t="n"/>
       <c r="E49" s="12" t="n"/>
     </row>
-    <row r="50" ht="13" customHeight="1" s="93">
+    <row r="50" ht="13" customHeight="1" s="102">
       <c r="A50" s="20" t="n"/>
       <c r="B50" s="4" t="n"/>
       <c r="C50" s="4" t="inlineStr">
@@ -2383,21 +2392,24 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Sales Margin</t>
-        </is>
-      </c>
-      <c r="E50" s="24" t="n"/>
-    </row>
-    <row r="51">
+          <t>PARAMS</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="n"/>
+    </row>
+    <row r="51" ht="13" customHeight="1" s="102">
+      <c r="A51" s="7" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Vega Weights</t>
+          <t>EVENTS</t>
         </is>
       </c>
       <c r="C51" s="3" t="n"/>
       <c r="D51" s="3" t="n"/>
-    </row>
-    <row r="52">
+      <c r="E51" s="9" t="n"/>
+    </row>
+    <row r="52" ht="13" customHeight="1" s="102">
+      <c r="A52" s="20" t="n"/>
       <c r="B52" s="4" t="n"/>
       <c r="C52" s="4" t="inlineStr">
         <is>
@@ -2405,6 +2417,29 @@
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>EVENTS</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="n"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Vega Weights</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="n"/>
+      <c r="D53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Table 1</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
         <is>
           <t>Vega Weights</t>
         </is>
@@ -2421,22 +2456,23 @@
     <hyperlink ref="D16" location="'NZDUSD'!R1C1" tooltip="" display="NZDUSD"/>
     <hyperlink ref="D18" location="'GBPUSD'!R1C1" tooltip="" display="GBPUSD"/>
     <hyperlink ref="D20" location="'GBPNZD'!R1C1" tooltip="" display="GBPNZD"/>
-    <hyperlink ref="D22" location="'USDHKD'!R1C1" tooltip="" display="USDHKD"/>
-    <hyperlink ref="D24" location="'GBPCNH'!R1C1" tooltip="" display="GBPCNH"/>
-    <hyperlink ref="D26" location="'AUDCNH'!R1C1" tooltip="" display="AUDCNH"/>
-    <hyperlink ref="D28" location="'NZDCNH'!R1C1" tooltip="" display="NZDCNH"/>
-    <hyperlink ref="D30" location="'CNHHKD'!R1C1" tooltip="" display="CNHHKD"/>
-    <hyperlink ref="D32" location="'EURCNH'!R1C1" tooltip="" display="EURCNH"/>
-    <hyperlink ref="D34" location="'AUDJPY'!R1C1" tooltip="" display="AUDJPY"/>
-    <hyperlink ref="D36" location="'EURJPY'!R1C1" tooltip="" display="EURJPY"/>
-    <hyperlink ref="D38" location="'EURUSD'!R1C1" tooltip="" display="EURUSD"/>
-    <hyperlink ref="D40" location="'AUDUSD'!R1C1" tooltip="" display="AUDUSD"/>
-    <hyperlink ref="D42" location="'USDJPY'!R1C1" tooltip="" display="USDJPY"/>
-    <hyperlink ref="D44" location="'USDCNH'!R1C1" tooltip="" display="USDCNH"/>
-    <hyperlink ref="D46" location="'USDCNY'!R1C1" tooltip="" display="USDCNY"/>
-    <hyperlink ref="D48" location="'PARAMS'!R1C1" tooltip="" display="PARAMS"/>
-    <hyperlink ref="D50" location="'Sales Margin'!R1C1" tooltip="" display="Sales Margin"/>
-    <hyperlink ref="D52" location="'Vega Weights'!R1C1" tooltip="" display="Vega Weights"/>
+    <hyperlink ref="D22" location="'EURGBP'!R1C1" tooltip="" display="EURGBP"/>
+    <hyperlink ref="D24" location="'USDHKD'!R1C1" tooltip="" display="USDHKD"/>
+    <hyperlink ref="D26" location="'GBPCNH'!R1C1" tooltip="" display="GBPCNH"/>
+    <hyperlink ref="D28" location="'AUDCNH'!R1C1" tooltip="" display="AUDCNH"/>
+    <hyperlink ref="D30" location="'NZDCNH'!R1C1" tooltip="" display="NZDCNH"/>
+    <hyperlink ref="D32" location="'CNHHKD'!R1C1" tooltip="" display="CNHHKD"/>
+    <hyperlink ref="D34" location="'EURCNH'!R1C1" tooltip="" display="EURCNH"/>
+    <hyperlink ref="D36" location="'AUDJPY'!R1C1" tooltip="" display="AUDJPY"/>
+    <hyperlink ref="D38" location="'EURJPY'!R1C1" tooltip="" display="EURJPY"/>
+    <hyperlink ref="D40" location="'EURUSD'!R1C1" tooltip="" display="EURUSD"/>
+    <hyperlink ref="D42" location="'AUDUSD'!R1C1" tooltip="" display="AUDUSD"/>
+    <hyperlink ref="D44" location="'USDJPY'!R1C1" tooltip="" display="USDJPY"/>
+    <hyperlink ref="D46" location="'USDCNH'!R1C1" tooltip="" display="USDCNH"/>
+    <hyperlink ref="D48" location="'USDCNY'!R1C1" tooltip="" display="USDCNY"/>
+    <hyperlink ref="D50" location="'PARAMS'!R1C1" tooltip="" display="PARAMS"/>
+    <hyperlink ref="D52" location="'EVENTS'!R1C1" tooltip="" display="EVENTS"/>
+    <hyperlink ref="D54" location="'Vega Weights'!R1C1" tooltip="" display="Vega Weights"/>
   </hyperlinks>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -2460,74 +2496,74 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="27" t="n"/>
       <c r="B1" s="27" t="n"/>
       <c r="C1" s="27" t="n"/>
       <c r="D1" s="27" t="n"/>
       <c r="E1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="27" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
       <c r="D2" s="27" t="n"/>
       <c r="E2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="27" t="n"/>
       <c r="B3" s="27" t="n"/>
       <c r="C3" s="27" t="n"/>
       <c r="D3" s="27" t="n"/>
       <c r="E3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="27" t="n"/>
       <c r="B4" s="27" t="n"/>
       <c r="C4" s="27" t="n"/>
       <c r="D4" s="27" t="n"/>
       <c r="E4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="27" t="n"/>
       <c r="B5" s="27" t="n"/>
       <c r="C5" s="27" t="n"/>
       <c r="D5" s="27" t="n"/>
       <c r="E5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="27" t="n"/>
       <c r="B6" s="27" t="n"/>
       <c r="C6" s="27" t="n"/>
       <c r="D6" s="27" t="n"/>
       <c r="E6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="27" t="n"/>
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="27" t="n"/>
       <c r="E7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="27" t="n"/>
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="27" t="n"/>
       <c r="E8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="27" t="n"/>
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="27" t="n"/>
       <c r="D9" s="27" t="n"/>
       <c r="E9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="27" t="n"/>
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="27" t="n"/>
@@ -2557,74 +2593,74 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="27" t="n"/>
       <c r="B1" s="27" t="n"/>
       <c r="C1" s="27" t="n"/>
       <c r="D1" s="27" t="n"/>
       <c r="E1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="27" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
       <c r="D2" s="27" t="n"/>
       <c r="E2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="27" t="n"/>
       <c r="B3" s="27" t="n"/>
       <c r="C3" s="27" t="n"/>
       <c r="D3" s="27" t="n"/>
       <c r="E3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="27" t="n"/>
       <c r="B4" s="27" t="n"/>
       <c r="C4" s="27" t="n"/>
       <c r="D4" s="27" t="n"/>
       <c r="E4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="27" t="n"/>
       <c r="B5" s="27" t="n"/>
       <c r="C5" s="27" t="n"/>
       <c r="D5" s="27" t="n"/>
       <c r="E5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="27" t="n"/>
       <c r="B6" s="27" t="n"/>
       <c r="C6" s="27" t="n"/>
       <c r="D6" s="27" t="n"/>
       <c r="E6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="27" t="n"/>
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="27" t="n"/>
       <c r="E7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="27" t="n"/>
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="27" t="n"/>
       <c r="E8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="27" t="n"/>
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="27" t="n"/>
       <c r="D9" s="27" t="n"/>
       <c r="E9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="27" t="n"/>
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="27" t="n"/>
@@ -2654,74 +2690,74 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="27" t="n"/>
       <c r="B1" s="27" t="n"/>
       <c r="C1" s="27" t="n"/>
       <c r="D1" s="27" t="n"/>
       <c r="E1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="27" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
       <c r="D2" s="27" t="n"/>
       <c r="E2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="27" t="n"/>
       <c r="B3" s="27" t="n"/>
       <c r="C3" s="27" t="n"/>
       <c r="D3" s="27" t="n"/>
       <c r="E3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="27" t="n"/>
       <c r="B4" s="27" t="n"/>
       <c r="C4" s="27" t="n"/>
       <c r="D4" s="27" t="n"/>
       <c r="E4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="27" t="n"/>
       <c r="B5" s="27" t="n"/>
       <c r="C5" s="27" t="n"/>
       <c r="D5" s="27" t="n"/>
       <c r="E5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="27" t="n"/>
       <c r="B6" s="27" t="n"/>
       <c r="C6" s="27" t="n"/>
       <c r="D6" s="27" t="n"/>
       <c r="E6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="27" t="n"/>
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="27" t="n"/>
       <c r="E7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="27" t="n"/>
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="27" t="n"/>
       <c r="E8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="27" t="n"/>
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="27" t="n"/>
       <c r="D9" s="27" t="n"/>
       <c r="E9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="27" t="n"/>
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="27" t="n"/>
@@ -2751,14 +2787,14 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="1"/>
-    <col width="8.351559999999999" customWidth="1" style="90" min="2" max="2"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="3" max="10"/>
-    <col width="13.5" customWidth="1" style="90" min="11" max="11"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="12" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="1"/>
+    <col width="8.351559999999999" customWidth="1" style="99" min="2" max="2"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="3" max="10"/>
+    <col width="13.5" customWidth="1" style="99" min="11" max="11"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="12" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -2791,13 +2827,13 @@
       <c r="J1" s="27" t="n"/>
       <c r="K1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="63">
         <f t="array" ref="B2">C2*3.4</f>
         <v>0.476</v>
       </c>
@@ -2807,24 +2843,24 @@
       <c r="D2" s="35" t="n">
         <v>0.0475</v>
       </c>
-      <c r="E2" s="53">
+      <c r="E2" s="63">
         <f t="array" ref="E2">D2*2.6</f>
         <v>0.1235</v>
       </c>
-      <c r="F2" s="54" t="n"/>
+      <c r="F2" s="64" t="n"/>
       <c r="G2" s="27" t="n"/>
       <c r="H2" s="27" t="n"/>
       <c r="I2" s="27" t="n"/>
       <c r="J2" s="27" t="n"/>
       <c r="K2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="53">
+      <c r="B3" s="63">
         <f t="array" ref="B3">C3*3.4</f>
         <v>0.4675</v>
       </c>
@@ -2834,24 +2870,24 @@
       <c r="D3" s="35" t="n">
         <v>0.1225</v>
       </c>
-      <c r="E3" s="53">
+      <c r="E3" s="63">
         <f t="array" ref="E3">D3*1.8</f>
         <v>0.2205</v>
       </c>
-      <c r="F3" s="54" t="n"/>
+      <c r="F3" s="64" t="n"/>
       <c r="G3" s="27" t="n"/>
       <c r="H3" s="27" t="n"/>
       <c r="I3" s="27" t="n"/>
       <c r="J3" s="27" t="n"/>
       <c r="K3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B4" s="53">
+      <c r="B4" s="63">
         <f t="array" ref="B4">C4*3.4</f>
         <v>0.5695</v>
       </c>
@@ -2861,24 +2897,24 @@
       <c r="D4" s="35" t="n">
         <v>0.26</v>
       </c>
-      <c r="E4" s="53">
+      <c r="E4" s="63">
         <f t="array" ref="E4">D4*1.8</f>
         <v>0.468</v>
       </c>
-      <c r="F4" s="54" t="n"/>
+      <c r="F4" s="64" t="n"/>
       <c r="G4" s="27" t="n"/>
       <c r="H4" s="27" t="n"/>
       <c r="I4" s="27" t="n"/>
       <c r="J4" s="27" t="n"/>
       <c r="K4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B5" s="53">
+      <c r="B5" s="63">
         <f t="array" ref="B5">C5*3.4</f>
         <v>0.663</v>
       </c>
@@ -2888,24 +2924,24 @@
       <c r="D5" s="35" t="n">
         <v>0.36</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="63">
         <f t="array" ref="E5">D5*1.8</f>
         <v>0.648</v>
       </c>
-      <c r="F5" s="54" t="n"/>
+      <c r="F5" s="64" t="n"/>
       <c r="G5" s="27" t="n"/>
       <c r="H5" s="27" t="n"/>
       <c r="I5" s="27" t="n"/>
       <c r="J5" s="27" t="n"/>
       <c r="K5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B6" s="53">
+      <c r="B6" s="63">
         <f t="array" ref="B6">C6*3.4</f>
         <v>0.765</v>
       </c>
@@ -2915,24 +2951,24 @@
       <c r="D6" s="35" t="n">
         <v>0.4625</v>
       </c>
-      <c r="E6" s="53">
+      <c r="E6" s="63">
         <f t="array" ref="E6">D6*1.8</f>
         <v>0.8325</v>
       </c>
-      <c r="F6" s="54" t="n"/>
+      <c r="F6" s="64" t="n"/>
       <c r="G6" s="27" t="n"/>
       <c r="H6" s="27" t="n"/>
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="27" t="n"/>
       <c r="K6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B7" s="53">
+      <c r="B7" s="63">
         <f t="array" ref="B7">C7*3.4</f>
         <v>0.867</v>
       </c>
@@ -2942,24 +2978,24 @@
       <c r="D7" s="35" t="n">
         <v>0.6775</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="63">
         <f t="array" ref="E7">D7*1.8</f>
         <v>1.2195</v>
       </c>
-      <c r="F7" s="54" t="n"/>
+      <c r="F7" s="64" t="n"/>
       <c r="G7" s="27" t="n"/>
       <c r="H7" s="27" t="n"/>
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="27" t="n"/>
       <c r="K7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B8" s="53">
+      <c r="B8" s="63">
         <f t="array" ref="B8">C8*3.4</f>
         <v>1.02</v>
       </c>
@@ -2969,24 +3005,24 @@
       <c r="D8" s="35" t="n">
         <v>0.57</v>
       </c>
-      <c r="E8" s="53">
+      <c r="E8" s="63">
         <f t="array" ref="E8">D8*1.8</f>
         <v>1.026</v>
       </c>
-      <c r="F8" s="54" t="n"/>
+      <c r="F8" s="64" t="n"/>
       <c r="G8" s="27" t="n"/>
       <c r="H8" s="27" t="n"/>
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="27" t="n"/>
       <c r="K8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B9" s="53">
+      <c r="B9" s="63">
         <f t="array" ref="B9">C9*3.4</f>
         <v>1.122</v>
       </c>
@@ -2996,24 +3032,24 @@
       <c r="D9" s="35" t="n">
         <v>0.925</v>
       </c>
-      <c r="E9" s="53">
+      <c r="E9" s="63">
         <f t="array" ref="E9">D9*1.8</f>
         <v>1.665</v>
       </c>
-      <c r="F9" s="54" t="n"/>
+      <c r="F9" s="64" t="n"/>
       <c r="G9" s="27" t="n"/>
       <c r="H9" s="27" t="n"/>
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="27" t="n"/>
       <c r="K9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B10" s="53">
+      <c r="B10" s="63">
         <f t="array" ref="B10">C10*3.4</f>
         <v>1.207</v>
       </c>
@@ -3023,23 +3059,23 @@
       <c r="D10" s="35" t="n">
         <v>1.1225</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="63">
         <f t="array" ref="E10">D10*1.8</f>
         <v>2.0205</v>
       </c>
-      <c r="F10" s="54" t="n"/>
+      <c r="F10" s="64" t="n"/>
       <c r="G10" s="27" t="n"/>
       <c r="H10" s="27" t="n"/>
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="27" t="n"/>
       <c r="K10" s="27" t="n"/>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="27" t="n"/>
-      <c r="B11" s="55" t="n"/>
+      <c r="B11" s="65" t="n"/>
       <c r="C11" s="27" t="n"/>
       <c r="D11" s="27" t="n"/>
-      <c r="E11" s="55" t="n"/>
+      <c r="E11" s="65" t="n"/>
       <c r="F11" s="27" t="n"/>
       <c r="G11" s="27" t="n"/>
       <c r="H11" s="27" t="n"/>
@@ -3047,7 +3083,7 @@
       <c r="J11" s="27" t="n"/>
       <c r="K11" s="27" t="n"/>
     </row>
-    <row r="12" ht="13.65" customHeight="1" s="93">
+    <row r="12" ht="13.65" customHeight="1" s="102">
       <c r="A12" s="27" t="n"/>
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="27" t="n"/>
@@ -3060,7 +3096,7 @@
       <c r="J12" s="27" t="n"/>
       <c r="K12" s="27" t="n"/>
     </row>
-    <row r="13" ht="13.65" customHeight="1" s="93">
+    <row r="13" ht="13.65" customHeight="1" s="102">
       <c r="A13" s="27" t="n"/>
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="27" t="n"/>
@@ -3073,7 +3109,7 @@
       <c r="J13" s="27" t="n"/>
       <c r="K13" s="27" t="n"/>
     </row>
-    <row r="14" ht="13.65" customHeight="1" s="93">
+    <row r="14" ht="13.65" customHeight="1" s="102">
       <c r="A14" s="27" t="n"/>
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="27" t="n"/>
@@ -3086,7 +3122,7 @@
       <c r="J14" s="27" t="n"/>
       <c r="K14" s="27" t="n"/>
     </row>
-    <row r="15" ht="13.65" customHeight="1" s="93">
+    <row r="15" ht="13.65" customHeight="1" s="102">
       <c r="A15" s="27" t="n"/>
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="27" t="n"/>
@@ -3099,7 +3135,7 @@
       <c r="J15" s="27" t="n"/>
       <c r="K15" s="27" t="n"/>
     </row>
-    <row r="16" ht="13.65" customHeight="1" s="93">
+    <row r="16" ht="13.65" customHeight="1" s="102">
       <c r="A16" s="27" t="n"/>
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="27" t="n"/>
@@ -3112,7 +3148,7 @@
       <c r="J16" s="27" t="n"/>
       <c r="K16" s="27" t="n"/>
     </row>
-    <row r="17" ht="13.65" customHeight="1" s="93">
+    <row r="17" ht="13.65" customHeight="1" s="102">
       <c r="A17" s="27" t="n"/>
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="27" t="n"/>
@@ -3125,7 +3161,7 @@
       <c r="J17" s="27" t="n"/>
       <c r="K17" s="27" t="n"/>
     </row>
-    <row r="18" ht="13.65" customHeight="1" s="93">
+    <row r="18" ht="13.65" customHeight="1" s="102">
       <c r="A18" s="27" t="n"/>
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="27" t="n"/>
@@ -3138,7 +3174,7 @@
       <c r="J18" s="27" t="n"/>
       <c r="K18" s="27" t="n"/>
     </row>
-    <row r="19" ht="13.65" customHeight="1" s="93">
+    <row r="19" ht="13.65" customHeight="1" s="102">
       <c r="A19" s="27" t="n"/>
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="27" t="n"/>
@@ -3151,7 +3187,7 @@
       <c r="J19" s="27" t="n"/>
       <c r="K19" s="27" t="n"/>
     </row>
-    <row r="20" ht="13.65" customHeight="1" s="93">
+    <row r="20" ht="13.65" customHeight="1" s="102">
       <c r="A20" s="27" t="n"/>
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="27" t="n"/>
@@ -3162,9 +3198,9 @@
       <c r="H20" s="27" t="n"/>
       <c r="I20" s="27" t="n"/>
       <c r="J20" s="27" t="n"/>
-      <c r="K20" s="102" t="n"/>
-    </row>
-    <row r="21" ht="13.65" customHeight="1" s="93">
+      <c r="K20" s="109" t="n"/>
+    </row>
+    <row r="21" ht="13.65" customHeight="1" s="102">
       <c r="A21" s="27" t="n"/>
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="27" t="n"/>
@@ -3175,9 +3211,9 @@
       <c r="H21" s="27" t="n"/>
       <c r="I21" s="27" t="n"/>
       <c r="J21" s="27" t="n"/>
-      <c r="K21" s="102" t="n"/>
-    </row>
-    <row r="22" ht="13.65" customHeight="1" s="93">
+      <c r="K21" s="109" t="n"/>
+    </row>
+    <row r="22" ht="13.65" customHeight="1" s="102">
       <c r="A22" s="27" t="n"/>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
@@ -3188,7 +3224,7 @@
       <c r="H22" s="27" t="n"/>
       <c r="I22" s="27" t="n"/>
       <c r="J22" s="27" t="n"/>
-      <c r="K22" s="102" t="n"/>
+      <c r="K22" s="109" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
@@ -3213,11 +3249,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -3244,13 +3280,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="68">
         <f t="array" ref="B2">C2*3.25</f>
         <v>0.706875</v>
       </c>
@@ -3260,18 +3296,18 @@
       <c r="D2" s="35" t="n">
         <v>-1.25</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="69">
         <f t="array" ref="E2">D2*1.825</f>
         <v>-2.28125</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="68">
         <f t="array" ref="B3">C3*3.25</f>
         <v>0.755625</v>
       </c>
@@ -3281,18 +3317,18 @@
       <c r="D3" s="35" t="n">
         <v>-1.2925</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="69">
         <f t="array" ref="E3">D3*1.825</f>
         <v>-2.3588125</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
       </c>
-      <c r="B4" s="58">
+      <c r="B4" s="68">
         <f t="array" ref="B4">C4*3.25</f>
         <v>1.105</v>
       </c>
@@ -3302,18 +3338,18 @@
       <c r="D4" s="35" t="n">
         <v>-1.2975</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="69">
         <f t="array" ref="E4">D4*1.825</f>
         <v>-2.3679375</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B5" s="58">
+      <c r="B5" s="68">
         <f t="array" ref="B5">C5*3.75</f>
         <v>0.965625</v>
       </c>
@@ -3323,18 +3359,18 @@
       <c r="D5" s="35" t="n">
         <v>-1.47</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="69">
         <f t="array" ref="E5">D5*1.825</f>
         <v>-2.68275</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="68">
         <f t="array" ref="B6">4*C6</f>
         <v>1.26</v>
       </c>
@@ -3344,18 +3380,18 @@
       <c r="D6" s="35" t="n">
         <v>-1.84</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="69">
         <f t="array" ref="E6">D6*1.825</f>
         <v>-3.358</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B7" s="58">
+      <c r="B7" s="68">
         <f t="array" ref="B7">4*C7</f>
         <v>1.41</v>
       </c>
@@ -3365,18 +3401,18 @@
       <c r="D7" s="35" t="n">
         <v>-2.1575</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="69">
         <f t="array" ref="E7">D7*1.825</f>
         <v>-3.9374375</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B8" s="58">
+      <c r="B8" s="68">
         <f t="array" ref="B8">4*C8</f>
         <v>1.68</v>
       </c>
@@ -3386,18 +3422,18 @@
       <c r="D8" s="35" t="n">
         <v>-2.5675</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="69">
         <f t="array" ref="E8">D8*1.825</f>
         <v>-4.6856875</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B9" s="58">
+      <c r="B9" s="68">
         <f t="array" ref="B9">4*C9</f>
         <v>1.87</v>
       </c>
@@ -3407,18 +3443,18 @@
       <c r="D9" s="35" t="n">
         <v>-2.735</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="69">
         <f t="array" ref="E9">D9*1.825</f>
         <v>-4.991375</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="68">
         <f t="array" ref="B10">4.25*C10</f>
         <v>2.135625</v>
       </c>
@@ -3428,18 +3464,18 @@
       <c r="D10" s="35" t="n">
         <v>-2.875</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="69">
         <f t="array" ref="E10">D10*1.825</f>
         <v>-5.246875</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="70">
         <f t="array" ref="B11">4.25*C11</f>
         <v>2.295</v>
       </c>
@@ -3449,7 +3485,7 @@
       <c r="D11" s="35" t="n">
         <v>-3.34</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="71">
         <f t="array" ref="E11">D11*1.825</f>
         <v>-6.0955</v>
       </c>
@@ -3477,11 +3513,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -3508,13 +3544,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="68">
         <f t="array" ref="B2">3.25*C2</f>
         <v>0.6175</v>
       </c>
@@ -3524,18 +3560,18 @@
       <c r="D2" s="35" t="n">
         <v>-0.43</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="69">
         <f t="array" ref="E2">D2*1.8</f>
         <v>-0.774</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="68">
         <f t="array" ref="B3">3.25*C3</f>
         <v>0.65</v>
       </c>
@@ -3545,18 +3581,18 @@
       <c r="D3" s="35" t="n">
         <v>-0.415</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="69">
         <f t="array" ref="E3">D3*1.8</f>
         <v>-0.747</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
       </c>
-      <c r="B4" s="58">
+      <c r="B4" s="68">
         <f t="array" ref="B4">3.25*C4</f>
         <v>0.6175</v>
       </c>
@@ -3566,18 +3602,18 @@
       <c r="D4" s="35" t="n">
         <v>-0.37</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="69">
         <f t="array" ref="E4">D4*1.8</f>
         <v>-0.666</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B5" s="58">
+      <c r="B5" s="68">
         <f t="array" ref="B5">3.25*C5</f>
         <v>0.76375</v>
       </c>
@@ -3587,18 +3623,18 @@
       <c r="D5" s="35" t="n">
         <v>-0.475</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="69">
         <f t="array" ref="E5">D5*1.8</f>
         <v>-0.855</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="68">
         <f t="array" ref="B6">3.25*C6</f>
         <v>0.869375</v>
       </c>
@@ -3608,18 +3644,18 @@
       <c r="D6" s="35" t="n">
         <v>-0.6625</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="69">
         <f t="array" ref="E6">D6*1.8</f>
         <v>-1.1925</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B7" s="58">
+      <c r="B7" s="68">
         <f t="array" ref="B7">3.25*C7</f>
         <v>0.950625</v>
       </c>
@@ -3629,18 +3665,18 @@
       <c r="D7" s="35" t="n">
         <v>-0.8275</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="69">
         <f t="array" ref="E7">D7*1.825</f>
         <v>-1.5101875</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B8" s="58">
+      <c r="B8" s="68">
         <f t="array" ref="B8">3.25*C8</f>
         <v>1.129375</v>
       </c>
@@ -3650,18 +3686,18 @@
       <c r="D8" s="35" t="n">
         <v>-1.0925</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="69">
         <f t="array" ref="E8">D8*1.825</f>
         <v>-1.9938125</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B9" s="58">
+      <c r="B9" s="68">
         <f t="array" ref="B9">3.25*C9</f>
         <v>1.259375</v>
       </c>
@@ -3671,18 +3707,18 @@
       <c r="D9" s="35" t="n">
         <v>-1.2925</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="69">
         <f t="array" ref="E9">D9*1.825</f>
         <v>-2.3588125</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="68">
         <f t="array" ref="B10">3.25*C10</f>
         <v>1.291875</v>
       </c>
@@ -3692,18 +3728,18 @@
       <c r="D10" s="35" t="n">
         <v>-1.3775</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="69">
         <f t="array" ref="E10">D10*1.825</f>
         <v>-2.5139375</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="70">
         <f t="array" ref="B11">3.25*C11</f>
         <v>1.3975</v>
       </c>
@@ -3713,7 +3749,7 @@
       <c r="D11" s="35" t="n">
         <v>-1.685</v>
       </c>
-      <c r="E11" s="63">
+      <c r="E11" s="73">
         <f t="array" ref="E11">D11*1.75</f>
         <v>-2.94875</v>
       </c>
@@ -3741,13 +3777,13 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="6.5" customWidth="1" style="90" min="1" max="1"/>
-    <col width="7.67188" customWidth="1" style="90" min="2" max="3"/>
-    <col width="7.85156" customWidth="1" style="90" min="4" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="6.5" customWidth="1" style="99" min="1" max="1"/>
+    <col width="7.67188" customWidth="1" style="99" min="2" max="3"/>
+    <col width="7.85156" customWidth="1" style="99" min="4" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -3774,7 +3810,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
@@ -3795,7 +3831,7 @@
         <v>-0.315</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
@@ -3816,7 +3852,7 @@
         <v>-0.28875</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
@@ -3837,7 +3873,7 @@
         <v>-0.310625</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
@@ -3858,7 +3894,7 @@
         <v>-0.214375</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
@@ -3879,7 +3915,7 @@
         <v>-0.179375</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
@@ -3900,7 +3936,7 @@
         <v>-0.1665</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
@@ -3921,7 +3957,7 @@
         <v>-0.072</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
@@ -3942,7 +3978,7 @@
         <v>0.0045625</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -3963,7 +3999,7 @@
         <v>0.04625</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -4007,13 +4043,13 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="6.5" customWidth="1" style="90" min="1" max="1"/>
-    <col width="7.67188" customWidth="1" style="90" min="2" max="3"/>
-    <col width="7.85156" customWidth="1" style="90" min="4" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="6.5" customWidth="1" style="99" min="1" max="1"/>
+    <col width="7.67188" customWidth="1" style="99" min="2" max="3"/>
+    <col width="7.85156" customWidth="1" style="99" min="4" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -4040,13 +4076,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="58">
+      <c r="B2" s="68">
         <f t="array" ref="B2">C2*3</f>
         <v>0.8175</v>
       </c>
@@ -4056,18 +4092,18 @@
       <c r="D2" s="35" t="n">
         <v>-0.9175</v>
       </c>
-      <c r="E2" s="59">
+      <c r="E2" s="69">
         <f t="array" ref="E2">D2*1.8</f>
         <v>-1.6515</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="58">
+      <c r="B3" s="68">
         <f t="array" ref="B3">C3*3</f>
         <v>0.8775</v>
       </c>
@@ -4077,18 +4113,18 @@
       <c r="D3" s="35" t="n">
         <v>-1.0425</v>
       </c>
-      <c r="E3" s="59">
+      <c r="E3" s="69">
         <f t="array" ref="E3">D3*1.8</f>
         <v>-1.8765</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
       </c>
-      <c r="B4" s="58">
+      <c r="B4" s="68">
         <f t="array" ref="B4">C4*3</f>
         <v>0.93</v>
       </c>
@@ -4098,18 +4134,18 @@
       <c r="D4" s="35" t="n">
         <v>-1.205</v>
       </c>
-      <c r="E4" s="59">
+      <c r="E4" s="69">
         <f t="array" ref="E4">D4*1.8</f>
         <v>-2.169</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B5" s="58">
+      <c r="B5" s="68">
         <f t="array" ref="B5">C5*3</f>
         <v>1.02</v>
       </c>
@@ -4119,18 +4155,18 @@
       <c r="D5" s="35" t="n">
         <v>-1.295</v>
       </c>
-      <c r="E5" s="59">
+      <c r="E5" s="69">
         <f t="array" ref="E5">D5*1.825</f>
         <v>-2.363375</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B6" s="58">
+      <c r="B6" s="68">
         <f t="array" ref="B6">C6*3</f>
         <v>1.11</v>
       </c>
@@ -4140,18 +4176,18 @@
       <c r="D6" s="35" t="n">
         <v>-1.425</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="69">
         <f t="array" ref="E6">D6*1.825</f>
         <v>-2.600625</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B7" s="58">
+      <c r="B7" s="68">
         <f t="array" ref="B7">C7*3</f>
         <v>1.1925</v>
       </c>
@@ -4161,18 +4197,18 @@
       <c r="D7" s="35" t="n">
         <v>-1.4875</v>
       </c>
-      <c r="E7" s="59">
+      <c r="E7" s="69">
         <f t="array" ref="E7">D7*1.825</f>
         <v>-2.7146875</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B8" s="58">
+      <c r="B8" s="68">
         <f t="array" ref="B8">C8*3</f>
         <v>1.3125</v>
       </c>
@@ -4182,18 +4218,18 @@
       <c r="D8" s="35" t="n">
         <v>-1.6475</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="69">
         <f t="array" ref="E8">D8*1.825</f>
         <v>-3.0066875</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B9" s="58">
+      <c r="B9" s="68">
         <f t="array" ref="B9">C9*3</f>
         <v>1.3575</v>
       </c>
@@ -4203,18 +4239,18 @@
       <c r="D9" s="35" t="n">
         <v>-1.7175</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="69">
         <f t="array" ref="E9">D9*1.85</f>
         <v>-3.177375</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B10" s="58">
+      <c r="B10" s="68">
         <f t="array" ref="B10">C10*3</f>
         <v>1.4025</v>
       </c>
@@ -4224,18 +4260,18 @@
       <c r="D10" s="35" t="n">
         <v>-1.7675</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="69">
         <f t="array" ref="E10">D10*1.85</f>
         <v>-3.269875</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B11" s="60">
+      <c r="B11" s="70">
         <f t="array" ref="B11">C11*3</f>
         <v>1.47</v>
       </c>
@@ -4245,7 +4281,7 @@
       <c r="D11" s="35" t="n">
         <v>-1.75</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="71">
         <f t="array" ref="E11">D11*1.85</f>
         <v>-3.2375</v>
       </c>
@@ -4273,13 +4309,13 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="6.5" customWidth="1" style="90" min="1" max="1"/>
-    <col width="7.67188" customWidth="1" style="90" min="2" max="3"/>
-    <col width="7.85156" customWidth="1" style="90" min="4" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="6.5" customWidth="1" style="99" min="1" max="1"/>
+    <col width="7.67188" customWidth="1" style="99" min="2" max="3"/>
+    <col width="7.85156" customWidth="1" style="99" min="4" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -4306,13 +4342,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="53">
+      <c r="B2" s="63">
         <f t="array" ref="B2">C2*3</f>
         <v>0.6525</v>
       </c>
@@ -4327,13 +4363,13 @@
         <v>-0.050875</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="53">
+      <c r="B3" s="63">
         <f t="array" ref="B3">C3*3</f>
         <v>0.675</v>
       </c>
@@ -4348,13 +4384,13 @@
         <v>-0.2035</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
       </c>
-      <c r="B4" s="53">
+      <c r="B4" s="63">
         <f t="array" ref="B4">C4*3</f>
         <v>0.735</v>
       </c>
@@ -4369,13 +4405,13 @@
         <v>-0.272875</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B5" s="53">
+      <c r="B5" s="63">
         <f t="array" ref="B5">C5*3</f>
         <v>0.72</v>
       </c>
@@ -4390,13 +4426,13 @@
         <v>-0.444</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B6" s="53">
+      <c r="B6" s="63">
         <f t="array" ref="B6">C6*3</f>
         <v>0.8025</v>
       </c>
@@ -4411,13 +4447,13 @@
         <v>-0.846375</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B7" s="53">
+      <c r="B7" s="63">
         <f t="array" ref="B7">C7*3</f>
         <v>0.87</v>
       </c>
@@ -4432,13 +4468,13 @@
         <v>-1.19325</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B8" s="53">
+      <c r="B8" s="63">
         <f t="array" ref="B8">C8*3</f>
         <v>0.99</v>
       </c>
@@ -4448,18 +4484,18 @@
       <c r="D8" s="35" t="n">
         <v>-0.9575</v>
       </c>
-      <c r="E8" s="67">
+      <c r="E8" s="77">
         <f t="array" ref="E8">D8*2</f>
         <v>-1.915</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B9" s="53">
+      <c r="B9" s="63">
         <f t="array" ref="B9">C9*3</f>
         <v>1.065</v>
       </c>
@@ -4474,13 +4510,13 @@
         <v>-2.0484375</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B10" s="68">
+      <c r="B10" s="78">
         <f t="array" ref="B10">3.25*C10</f>
         <v>1.2025</v>
       </c>
@@ -4495,13 +4531,13 @@
         <v>-2.23125</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B11" s="69">
+      <c r="B11" s="79">
         <f t="array" ref="B11">3.5*C11</f>
         <v>1.4525</v>
       </c>
@@ -4539,21 +4575,21 @@
   <dimension ref="A1:U30"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="6.5" customWidth="1" style="90" min="1" max="1"/>
-    <col width="7.67188" customWidth="1" style="90" min="2" max="3"/>
-    <col width="7.85156" customWidth="1" style="90" min="4" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="7"/>
-    <col width="10.3516" customWidth="1" style="90" min="8" max="8"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="9" max="11"/>
-    <col width="12.8516" customWidth="1" style="90" min="12" max="12"/>
-    <col width="15" customWidth="1" style="90" min="13" max="13"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="14" max="14"/>
-    <col width="12.8516" customWidth="1" style="90" min="15" max="15"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="16" max="21"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="22" max="16384"/>
+    <col width="6.5" customWidth="1" style="99" min="1" max="1"/>
+    <col width="7.67188" customWidth="1" style="99" min="2" max="3"/>
+    <col width="7.85156" customWidth="1" style="99" min="4" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="7"/>
+    <col width="10.3516" customWidth="1" style="99" min="8" max="8"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="9" max="11"/>
+    <col width="12.8516" customWidth="1" style="99" min="12" max="12"/>
+    <col width="15" customWidth="1" style="99" min="13" max="13"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="14" max="14"/>
+    <col width="12.8516" customWidth="1" style="99" min="15" max="15"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="16" max="21"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="22" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -4596,27 +4632,27 @@
       <c r="T1" s="27" t="n"/>
       <c r="U1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="96">
+      <c r="B2" s="103">
         <f t="array" ref="B2">C2*3.4</f>
         <v>0.6205</v>
       </c>
-      <c r="C2" s="97" t="n">
+      <c r="C2" s="104" t="n">
         <v>0.1825</v>
       </c>
-      <c r="D2" s="98" t="n">
+      <c r="D2" s="105" t="n">
         <v>0.385</v>
       </c>
-      <c r="E2" s="96">
+      <c r="E2" s="103">
         <f t="array" ref="E2">D2*2.05</f>
         <v>0.78925</v>
       </c>
-      <c r="F2" s="54" t="n"/>
+      <c r="F2" s="64" t="n"/>
       <c r="G2" s="27" t="n"/>
       <c r="H2" s="27" t="n"/>
       <c r="I2" s="27" t="n"/>
@@ -4633,27 +4669,27 @@
       <c r="T2" s="27" t="n"/>
       <c r="U2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="96">
+      <c r="B3" s="103">
         <f t="array" ref="B3">C3*3.4</f>
         <v>0.6375</v>
       </c>
-      <c r="C3" s="97" t="n">
+      <c r="C3" s="104" t="n">
         <v>0.1875</v>
       </c>
-      <c r="D3" s="98" t="n">
+      <c r="D3" s="105" t="n">
         <v>0.45</v>
       </c>
-      <c r="E3" s="96">
+      <c r="E3" s="103">
         <f t="array" ref="E3">D3*2.15</f>
         <v>0.9675</v>
       </c>
-      <c r="F3" s="54" t="n"/>
+      <c r="F3" s="64" t="n"/>
       <c r="G3" s="27" t="n"/>
       <c r="H3" s="27" t="n"/>
       <c r="I3" s="27" t="n"/>
@@ -4670,27 +4706,27 @@
       <c r="T3" s="27" t="n"/>
       <c r="U3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B4" s="96">
+      <c r="B4" s="103">
         <f t="array" ref="B4">C4*3.4</f>
         <v>0.731</v>
       </c>
-      <c r="C4" s="97" t="n">
+      <c r="C4" s="104" t="n">
         <v>0.215</v>
       </c>
-      <c r="D4" s="98" t="n">
+      <c r="D4" s="105" t="n">
         <v>0.525</v>
       </c>
-      <c r="E4" s="96">
+      <c r="E4" s="103">
         <f t="array" ref="E4">D4*2.3</f>
         <v>1.2075</v>
       </c>
-      <c r="F4" s="54" t="n"/>
+      <c r="F4" s="64" t="n"/>
       <c r="G4" s="27" t="n"/>
       <c r="H4" s="27" t="n"/>
       <c r="I4" s="27" t="n"/>
@@ -4707,27 +4743,27 @@
       <c r="T4" s="27" t="n"/>
       <c r="U4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B5" s="96">
+      <c r="B5" s="103">
         <f t="array" ref="B5">C5*3.4</f>
         <v>0.816</v>
       </c>
-      <c r="C5" s="97" t="n">
+      <c r="C5" s="104" t="n">
         <v>0.24</v>
       </c>
-      <c r="D5" s="98" t="n">
+      <c r="D5" s="105" t="n">
         <v>0.66</v>
       </c>
-      <c r="E5" s="96">
+      <c r="E5" s="103">
         <f t="array" ref="E5">D5*2.3</f>
         <v>1.518</v>
       </c>
-      <c r="F5" s="54" t="n"/>
+      <c r="F5" s="64" t="n"/>
       <c r="G5" s="27" t="n"/>
       <c r="H5" s="27" t="n"/>
       <c r="I5" s="27" t="n"/>
@@ -4744,33 +4780,33 @@
       <c r="T5" s="27" t="n"/>
       <c r="U5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B6" s="96">
+      <c r="B6" s="103">
         <f t="array" ref="B6">C6*3.4</f>
         <v>0.867</v>
       </c>
-      <c r="C6" s="97" t="n">
+      <c r="C6" s="104" t="n">
         <v>0.255</v>
       </c>
-      <c r="D6" s="98" t="n">
+      <c r="D6" s="105" t="n">
         <v>0.74</v>
       </c>
-      <c r="E6" s="96">
+      <c r="E6" s="103">
         <f t="array" ref="E6">D6*2.3</f>
         <v>1.702</v>
       </c>
-      <c r="F6" s="54" t="n"/>
+      <c r="F6" s="64" t="n"/>
       <c r="G6" s="27" t="n"/>
       <c r="H6" s="27" t="n"/>
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="27" t="n"/>
       <c r="K6" s="27" t="n"/>
-      <c r="L6" s="103" t="n"/>
+      <c r="L6" s="110" t="n"/>
       <c r="M6" s="27" t="n"/>
       <c r="N6" s="27" t="n"/>
       <c r="O6" s="27" t="n"/>
@@ -4781,27 +4817,27 @@
       <c r="T6" s="27" t="n"/>
       <c r="U6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B7" s="96">
+      <c r="B7" s="103">
         <f t="array" ref="B7">C7*3.4</f>
         <v>0.986</v>
       </c>
-      <c r="C7" s="97" t="n">
+      <c r="C7" s="104" t="n">
         <v>0.29</v>
       </c>
-      <c r="D7" s="98" t="n">
+      <c r="D7" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="E7" s="96">
+      <c r="E7" s="103">
         <f t="array" ref="E7">D7*2.3</f>
         <v>2.185</v>
       </c>
-      <c r="F7" s="54" t="n"/>
+      <c r="F7" s="64" t="n"/>
       <c r="G7" s="27" t="n"/>
       <c r="H7" s="27" t="n"/>
       <c r="I7" s="27" t="n"/>
@@ -4818,33 +4854,33 @@
       <c r="T7" s="27" t="n"/>
       <c r="U7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B8" s="96">
+      <c r="B8" s="103">
         <f t="array" ref="B8">C8*3.4</f>
         <v>1.122</v>
       </c>
-      <c r="C8" s="97" t="n">
+      <c r="C8" s="104" t="n">
         <v>0.33</v>
       </c>
-      <c r="D8" s="98" t="n">
+      <c r="D8" s="105" t="n">
         <v>1.07</v>
       </c>
-      <c r="E8" s="96">
+      <c r="E8" s="103">
         <f t="array" ref="E8">D8*2.3</f>
         <v>2.461</v>
       </c>
-      <c r="F8" s="54" t="n"/>
+      <c r="F8" s="64" t="n"/>
       <c r="G8" s="27" t="n"/>
       <c r="H8" s="27" t="n"/>
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="27" t="n"/>
       <c r="K8" s="27" t="n"/>
-      <c r="L8" s="104" t="n"/>
+      <c r="L8" s="111" t="n"/>
       <c r="M8" s="27" t="n"/>
       <c r="N8" s="27" t="n"/>
       <c r="O8" s="27" t="n"/>
@@ -4855,27 +4891,27 @@
       <c r="T8" s="27" t="n"/>
       <c r="U8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B9" s="96">
+      <c r="B9" s="103">
         <f t="array" ref="B9">C9*3.4</f>
         <v>1.207</v>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="C9" s="104" t="n">
         <v>0.355</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D9" s="105" t="n">
         <v>1.15</v>
       </c>
-      <c r="E9" s="96">
+      <c r="E9" s="103">
         <f t="array" ref="E9">D9*2.3</f>
         <v>2.645</v>
       </c>
-      <c r="F9" s="54" t="n"/>
+      <c r="F9" s="64" t="n"/>
       <c r="G9" s="27" t="n"/>
       <c r="H9" s="27" t="n"/>
       <c r="I9" s="27" t="n"/>
@@ -4884,7 +4920,7 @@
       <c r="L9" s="27" t="n"/>
       <c r="M9" s="27" t="n"/>
       <c r="N9" s="27" t="n"/>
-      <c r="O9" s="105" t="n"/>
+      <c r="O9" s="112" t="n"/>
       <c r="P9" s="27" t="n"/>
       <c r="Q9" s="27" t="n"/>
       <c r="R9" s="27" t="n"/>
@@ -4892,27 +4928,27 @@
       <c r="T9" s="27" t="n"/>
       <c r="U9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B10" s="96">
+      <c r="B10" s="103">
         <f t="array" ref="B10">C10*3.4</f>
         <v>1.292</v>
       </c>
-      <c r="C10" s="97" t="n">
+      <c r="C10" s="104" t="n">
         <v>0.38</v>
       </c>
-      <c r="D10" s="98" t="n">
+      <c r="D10" s="105" t="n">
         <v>1.25</v>
       </c>
-      <c r="E10" s="96">
+      <c r="E10" s="103">
         <f t="array" ref="E10">D10*2.3</f>
         <v>2.875</v>
       </c>
-      <c r="F10" s="54" t="n"/>
+      <c r="F10" s="64" t="n"/>
       <c r="G10" s="27" t="n"/>
       <c r="H10" s="27" t="n"/>
       <c r="I10" s="27" t="n"/>
@@ -4921,7 +4957,7 @@
       <c r="L10" s="27" t="n"/>
       <c r="M10" s="27" t="n"/>
       <c r="N10" s="27" t="n"/>
-      <c r="O10" s="106" t="n"/>
+      <c r="O10" s="113" t="n"/>
       <c r="P10" s="27" t="n"/>
       <c r="Q10" s="27" t="n"/>
       <c r="R10" s="27" t="n"/>
@@ -4929,12 +4965,12 @@
       <c r="T10" s="27" t="n"/>
       <c r="U10" s="27" t="n"/>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="27" t="n"/>
-      <c r="B11" s="55" t="n"/>
+      <c r="B11" s="65" t="n"/>
       <c r="C11" s="27" t="n"/>
       <c r="D11" s="27" t="n"/>
-      <c r="E11" s="55" t="n"/>
+      <c r="E11" s="65" t="n"/>
       <c r="F11" s="27" t="n"/>
       <c r="G11" s="27" t="n"/>
       <c r="H11" s="27" t="n"/>
@@ -4952,7 +4988,7 @@
       <c r="T11" s="27" t="n"/>
       <c r="U11" s="27" t="n"/>
     </row>
-    <row r="12" ht="13.65" customHeight="1" s="93">
+    <row r="12" ht="13.65" customHeight="1" s="102">
       <c r="A12" s="27" t="n"/>
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="27" t="n"/>
@@ -4972,10 +5008,10 @@
       <c r="Q12" s="27" t="n"/>
       <c r="R12" s="27" t="n"/>
       <c r="S12" s="27" t="n"/>
-      <c r="T12" s="104" t="n"/>
-      <c r="U12" s="105" t="n"/>
-    </row>
-    <row r="13" ht="13.65" customHeight="1" s="93">
+      <c r="T12" s="111" t="n"/>
+      <c r="U12" s="112" t="n"/>
+    </row>
+    <row r="13" ht="13.65" customHeight="1" s="102">
       <c r="A13" s="27" t="n"/>
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="27" t="n"/>
@@ -4995,10 +5031,10 @@
       <c r="Q13" s="27" t="n"/>
       <c r="R13" s="27" t="n"/>
       <c r="S13" s="27" t="n"/>
-      <c r="T13" s="104" t="n"/>
+      <c r="T13" s="111" t="n"/>
       <c r="U13" s="27" t="n"/>
     </row>
-    <row r="14" ht="13.65" customHeight="1" s="93">
+    <row r="14" ht="13.65" customHeight="1" s="102">
       <c r="A14" s="27" t="n"/>
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="27" t="n"/>
@@ -5021,7 +5057,7 @@
       <c r="T14" s="27" t="n"/>
       <c r="U14" s="27" t="n"/>
     </row>
-    <row r="15" ht="13.65" customHeight="1" s="93">
+    <row r="15" ht="13.65" customHeight="1" s="102">
       <c r="A15" s="27" t="n"/>
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="27" t="n"/>
@@ -5044,7 +5080,7 @@
       <c r="T15" s="27" t="n"/>
       <c r="U15" s="27" t="n"/>
     </row>
-    <row r="16" ht="13.65" customHeight="1" s="93">
+    <row r="16" ht="13.65" customHeight="1" s="102">
       <c r="A16" s="27" t="n"/>
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="27" t="n"/>
@@ -5067,7 +5103,7 @@
       <c r="T16" s="27" t="n"/>
       <c r="U16" s="27" t="n"/>
     </row>
-    <row r="17" ht="13.65" customHeight="1" s="93">
+    <row r="17" ht="13.65" customHeight="1" s="102">
       <c r="A17" s="27" t="n"/>
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="27" t="n"/>
@@ -5090,7 +5126,7 @@
       <c r="T17" s="27" t="n"/>
       <c r="U17" s="27" t="n"/>
     </row>
-    <row r="18" ht="13.65" customHeight="1" s="93">
+    <row r="18" ht="13.65" customHeight="1" s="102">
       <c r="A18" s="27" t="n"/>
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="27" t="n"/>
@@ -5113,7 +5149,7 @@
       <c r="T18" s="27" t="n"/>
       <c r="U18" s="27" t="n"/>
     </row>
-    <row r="19" ht="13.65" customHeight="1" s="93">
+    <row r="19" ht="13.65" customHeight="1" s="102">
       <c r="A19" s="27" t="n"/>
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="27" t="n"/>
@@ -5123,7 +5159,7 @@
       <c r="G19" s="27" t="n"/>
       <c r="H19" s="27" t="n"/>
       <c r="I19" s="27" t="n"/>
-      <c r="J19" s="107" t="n"/>
+      <c r="J19" s="114" t="n"/>
       <c r="K19" s="27" t="n"/>
       <c r="L19" s="27" t="n"/>
       <c r="M19" s="27" t="n"/>
@@ -5136,7 +5172,7 @@
       <c r="T19" s="27" t="n"/>
       <c r="U19" s="27" t="n"/>
     </row>
-    <row r="20" ht="13.65" customHeight="1" s="93">
+    <row r="20" ht="13.65" customHeight="1" s="102">
       <c r="A20" s="27" t="n"/>
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="27" t="n"/>
@@ -5148,7 +5184,7 @@
       <c r="I20" s="27" t="n"/>
       <c r="J20" s="27" t="n"/>
       <c r="K20" s="27" t="n"/>
-      <c r="L20" s="104" t="n"/>
+      <c r="L20" s="111" t="n"/>
       <c r="M20" s="27" t="n"/>
       <c r="N20" s="27" t="n"/>
       <c r="O20" s="27" t="n"/>
@@ -5159,7 +5195,7 @@
       <c r="T20" s="27" t="n"/>
       <c r="U20" s="27" t="n"/>
     </row>
-    <row r="21" ht="13.65" customHeight="1" s="93">
+    <row r="21" ht="13.65" customHeight="1" s="102">
       <c r="A21" s="27" t="n"/>
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="27" t="n"/>
@@ -5171,7 +5207,7 @@
       <c r="I21" s="27" t="n"/>
       <c r="J21" s="27" t="n"/>
       <c r="K21" s="27" t="n"/>
-      <c r="L21" s="108" t="n"/>
+      <c r="L21" s="115" t="n"/>
       <c r="M21" s="27" t="n"/>
       <c r="N21" s="27" t="n"/>
       <c r="O21" s="27" t="n"/>
@@ -5182,7 +5218,7 @@
       <c r="T21" s="27" t="n"/>
       <c r="U21" s="27" t="n"/>
     </row>
-    <row r="22" ht="13.65" customHeight="1" s="93">
+    <row r="22" ht="13.65" customHeight="1" s="102">
       <c r="A22" s="27" t="n"/>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
@@ -5205,7 +5241,7 @@
       <c r="T22" s="27" t="n"/>
       <c r="U22" s="27" t="n"/>
     </row>
-    <row r="23" ht="13.65" customHeight="1" s="93">
+    <row r="23" ht="13.65" customHeight="1" s="102">
       <c r="A23" s="27" t="n"/>
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="27" t="n"/>
@@ -5228,7 +5264,7 @@
       <c r="T23" s="27" t="n"/>
       <c r="U23" s="27" t="n"/>
     </row>
-    <row r="24" ht="13.65" customHeight="1" s="93">
+    <row r="24" ht="13.65" customHeight="1" s="102">
       <c r="A24" s="27" t="n"/>
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="27" t="n"/>
@@ -5251,7 +5287,7 @@
       <c r="T24" s="27" t="n"/>
       <c r="U24" s="27" t="n"/>
     </row>
-    <row r="25" ht="13.65" customHeight="1" s="93">
+    <row r="25" ht="13.65" customHeight="1" s="102">
       <c r="A25" s="27" t="n"/>
       <c r="B25" s="27" t="n"/>
       <c r="C25" s="27" t="n"/>
@@ -5274,7 +5310,7 @@
       <c r="T25" s="27" t="n"/>
       <c r="U25" s="27" t="n"/>
     </row>
-    <row r="26" ht="13.65" customHeight="1" s="93">
+    <row r="26" ht="13.65" customHeight="1" s="102">
       <c r="A26" s="27" t="n"/>
       <c r="B26" s="27" t="n"/>
       <c r="C26" s="27" t="n"/>
@@ -5297,7 +5333,7 @@
       <c r="T26" s="27" t="n"/>
       <c r="U26" s="27" t="n"/>
     </row>
-    <row r="27" ht="13.65" customHeight="1" s="93">
+    <row r="27" ht="13.65" customHeight="1" s="102">
       <c r="A27" s="27" t="n"/>
       <c r="B27" s="27" t="n"/>
       <c r="C27" s="27" t="n"/>
@@ -5320,7 +5356,7 @@
       <c r="T27" s="27" t="n"/>
       <c r="U27" s="27" t="n"/>
     </row>
-    <row r="28" ht="13.65" customHeight="1" s="93">
+    <row r="28" ht="13.65" customHeight="1" s="102">
       <c r="A28" s="27" t="n"/>
       <c r="B28" s="27" t="n"/>
       <c r="C28" s="27" t="n"/>
@@ -5343,7 +5379,7 @@
       <c r="T28" s="27" t="n"/>
       <c r="U28" s="27" t="n"/>
     </row>
-    <row r="29" ht="13.65" customHeight="1" s="93">
+    <row r="29" ht="13.65" customHeight="1" s="102">
       <c r="A29" s="27" t="n"/>
       <c r="B29" s="27" t="n"/>
       <c r="C29" s="27" t="n"/>
@@ -5366,7 +5402,7 @@
       <c r="T29" s="27" t="n"/>
       <c r="U29" s="27" t="n"/>
     </row>
-    <row r="30" ht="13.65" customHeight="1" s="93">
+    <row r="30" ht="13.65" customHeight="1" s="102">
       <c r="A30" s="27" t="n"/>
       <c r="B30" s="27" t="n"/>
       <c r="C30" s="27" t="n"/>
@@ -5378,7 +5414,7 @@
       <c r="I30" s="27" t="n"/>
       <c r="J30" s="27" t="n"/>
       <c r="K30" s="27" t="n"/>
-      <c r="L30" s="104" t="n"/>
+      <c r="L30" s="111" t="n"/>
       <c r="M30" s="27" t="n"/>
       <c r="N30" s="27" t="n"/>
       <c r="O30" s="27" t="n"/>
@@ -5412,11 +5448,11 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="26" t="inlineStr">
         <is>
           <t>indication.xlsx</t>
@@ -5427,63 +5463,63 @@
       <c r="D1" s="27" t="n"/>
       <c r="E1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="27" t="n"/>
       <c r="B2" s="27" t="n"/>
       <c r="C2" s="27" t="n"/>
       <c r="D2" s="27" t="n"/>
       <c r="E2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="27" t="n"/>
       <c r="B3" s="27" t="n"/>
       <c r="C3" s="27" t="n"/>
       <c r="D3" s="27" t="n"/>
       <c r="E3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="27" t="n"/>
       <c r="B4" s="27" t="n"/>
       <c r="C4" s="27" t="n"/>
       <c r="D4" s="27" t="n"/>
       <c r="E4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="27" t="n"/>
       <c r="B5" s="27" t="n"/>
       <c r="C5" s="27" t="n"/>
       <c r="D5" s="27" t="n"/>
       <c r="E5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="27" t="n"/>
       <c r="B6" s="27" t="n"/>
       <c r="C6" s="27" t="n"/>
       <c r="D6" s="27" t="n"/>
       <c r="E6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="27" t="n"/>
       <c r="B7" s="27" t="n"/>
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="27" t="n"/>
       <c r="E7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="27" t="n"/>
       <c r="B8" s="27" t="n"/>
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="27" t="n"/>
       <c r="E8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="27" t="n"/>
       <c r="B9" s="27" t="n"/>
       <c r="C9" s="27" t="n"/>
       <c r="D9" s="27" t="n"/>
       <c r="E9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="27" t="n"/>
       <c r="B10" s="27" t="n"/>
       <c r="C10" s="27" t="n"/>
@@ -5513,11 +5549,11 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -5544,191 +5580,191 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="96">
+      <c r="B2" s="103">
         <f t="array" ref="B2">C2*1.4</f>
         <v>0.546</v>
       </c>
-      <c r="C2" s="97" t="n">
+      <c r="C2" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D2" s="98" t="n">
+      <c r="D2" s="105" t="n">
         <v>0.5</v>
       </c>
-      <c r="E2" s="99">
+      <c r="E2" s="106">
         <f t="array" ref="E2">D2*1.2</f>
         <v>0.6</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="96">
+      <c r="B3" s="103">
         <f t="array" ref="B3">C3*1.4</f>
         <v>0.546</v>
       </c>
-      <c r="C3" s="97" t="n">
+      <c r="C3" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D3" s="98" t="n">
+      <c r="D3" s="105" t="n">
         <v>0.515</v>
       </c>
-      <c r="E3" s="99">
+      <c r="E3" s="106">
         <f t="array" ref="E3">D3*1.2</f>
         <v>0.618</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B4" s="96">
+      <c r="B4" s="103">
         <f t="array" ref="B4">C4*1.4</f>
         <v>0.546</v>
       </c>
-      <c r="C4" s="97" t="n">
+      <c r="C4" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D4" s="98" t="n">
+      <c r="D4" s="105" t="n">
         <v>0.55</v>
       </c>
-      <c r="E4" s="99">
+      <c r="E4" s="106">
         <f t="array" ref="E4">D4*1.2</f>
         <v>0.66</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B5" s="96">
+      <c r="B5" s="103">
         <f t="array" ref="B5">C5*1.4</f>
         <v>0.546</v>
       </c>
-      <c r="C5" s="97" t="n">
+      <c r="C5" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D5" s="98" t="n">
+      <c r="D5" s="105" t="n">
         <v>0.525</v>
       </c>
-      <c r="E5" s="99">
+      <c r="E5" s="106">
         <f t="array" ref="E5">D5*1.2</f>
         <v>0.63</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B6" s="96">
+      <c r="B6" s="103">
         <f t="array" ref="B6">C6*1.55</f>
         <v>0.6045</v>
       </c>
-      <c r="C6" s="97" t="n">
+      <c r="C6" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D6" s="98" t="n">
+      <c r="D6" s="105" t="n">
         <v>0.525</v>
       </c>
-      <c r="E6" s="99">
+      <c r="E6" s="106">
         <f t="array" ref="E6">D6*1.3</f>
         <v>0.6825</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B7" s="96">
+      <c r="B7" s="103">
         <f t="array" ref="B7">C7*1.65</f>
         <v>0.6435</v>
       </c>
-      <c r="C7" s="97" t="n">
+      <c r="C7" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D7" s="98" t="n">
+      <c r="D7" s="105" t="n">
         <v>0.6</v>
       </c>
-      <c r="E7" s="99">
+      <c r="E7" s="106">
         <f t="array" ref="E7">D7*1.4</f>
         <v>0.84</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B8" s="96">
+      <c r="B8" s="103">
         <f t="array" ref="B8">C8*1.75</f>
         <v>0.6825</v>
       </c>
-      <c r="C8" s="97" t="n">
+      <c r="C8" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D8" s="98" t="n">
+      <c r="D8" s="105" t="n">
         <v>0.625</v>
       </c>
-      <c r="E8" s="99">
+      <c r="E8" s="106">
         <f t="array" ref="E8">D8*1.5</f>
         <v>0.9375</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B9" s="96">
+      <c r="B9" s="103">
         <f t="array" ref="B9">C9*1.75</f>
         <v>0.6825</v>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="C9" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D9" s="105" t="n">
         <v>0.65</v>
       </c>
-      <c r="E9" s="99">
+      <c r="E9" s="106">
         <f t="array" ref="E9">D9*1.5</f>
         <v>0.975</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B10" s="100">
+      <c r="B10" s="107">
         <f t="array" ref="B10">C10*1.75</f>
         <v>0.6825</v>
       </c>
-      <c r="C10" s="97" t="n">
+      <c r="C10" s="104" t="n">
         <v>0.39</v>
       </c>
-      <c r="D10" s="98" t="n">
+      <c r="D10" s="105" t="n">
         <v>0.65</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="108">
         <f t="array" ref="E10">D10*1.5</f>
         <v>0.975</v>
       </c>
@@ -5753,16 +5789,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S26"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.8333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="15.1719" customWidth="1" style="90" min="1" max="1"/>
-    <col width="10.8516" customWidth="1" style="90" min="2" max="14"/>
-    <col width="11.8516" customWidth="1" style="90" min="15" max="19"/>
-    <col width="11.8516" customWidth="1" style="90" min="20" max="16384"/>
+    <col width="15.1719" customWidth="1" style="99" min="1" max="1"/>
+    <col width="10.8516" customWidth="1" style="99" min="2" max="14"/>
+    <col width="11.8516" customWidth="1" style="99" min="15" max="19"/>
+    <col width="11.8516" customWidth="1" style="99" min="20" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="27" t="n"/>
       <c r="B1" s="29" t="inlineStr">
         <is>
@@ -5779,12 +5815,12 @@
           <t>EURCNH</t>
         </is>
       </c>
-      <c r="E1" s="79" t="inlineStr">
+      <c r="E1" s="89" t="inlineStr">
         <is>
           <t>GBPCNH</t>
         </is>
       </c>
-      <c r="F1" s="80" t="inlineStr">
+      <c r="F1" s="90" t="inlineStr">
         <is>
           <t>USDJPY</t>
         </is>
@@ -5839,52 +5875,52 @@
       <c r="R1" s="27" t="n"/>
       <c r="S1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="29" t="inlineStr">
         <is>
           <t>initial</t>
         </is>
       </c>
-      <c r="B2" s="81" t="n">
+      <c r="B2" s="91" t="n">
         <v>4.9</v>
       </c>
-      <c r="C2" s="81" t="n">
+      <c r="C2" s="91" t="n">
         <v>5</v>
       </c>
-      <c r="D2" s="81" t="n">
+      <c r="D2" s="91" t="n">
         <v>0.42</v>
       </c>
-      <c r="E2" s="82" t="n">
+      <c r="E2" s="92" t="n">
         <v>0.5</v>
       </c>
-      <c r="F2" s="83" t="n">
+      <c r="F2" s="93" t="n">
         <v>6.05</v>
       </c>
-      <c r="G2" s="81" t="n">
+      <c r="G2" s="91" t="n">
         <v>6.25</v>
       </c>
-      <c r="H2" s="81" t="n">
+      <c r="H2" s="91" t="n">
         <v>10.9</v>
       </c>
-      <c r="I2" s="81" t="n">
+      <c r="I2" s="91" t="n">
         <v>7.75</v>
       </c>
-      <c r="J2" s="81" t="n">
+      <c r="J2" s="91" t="n">
         <v>10.9</v>
       </c>
-      <c r="K2" s="81" t="n">
+      <c r="K2" s="91" t="n">
         <v>0.37</v>
       </c>
-      <c r="L2" s="81" t="n">
+      <c r="L2" s="91" t="n">
         <v>0.405</v>
       </c>
-      <c r="M2" s="81" t="n">
+      <c r="M2" s="91" t="n">
         <v>0.705</v>
       </c>
-      <c r="N2" s="81" t="n">
+      <c r="N2" s="91" t="n">
         <v>0.57</v>
       </c>
-      <c r="O2" s="81" t="n">
+      <c r="O2" s="91" t="n">
         <v>0.57</v>
       </c>
       <c r="P2" s="27" t="n"/>
@@ -5892,52 +5928,52 @@
       <c r="R2" s="27" t="n"/>
       <c r="S2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="29" t="inlineStr">
         <is>
           <t>long term</t>
         </is>
       </c>
-      <c r="B3" s="81" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="C3" s="81" t="n">
+      <c r="B3" s="91" t="n">
+        <v>6.800000000000001</v>
+      </c>
+      <c r="C3" s="91" t="n">
         <v>4.95</v>
       </c>
-      <c r="D3" s="81" t="n">
+      <c r="D3" s="91" t="n">
         <v>0.39</v>
       </c>
-      <c r="E3" s="82" t="n">
+      <c r="E3" s="92" t="n">
         <v>0.375</v>
       </c>
-      <c r="F3" s="83" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="G3" s="81" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="H3" s="81" t="n">
+      <c r="F3" s="93" t="n">
+        <v>7.649999999999999</v>
+      </c>
+      <c r="G3" s="91" t="n">
+        <v>6.950000000000001</v>
+      </c>
+      <c r="H3" s="91" t="n">
         <v>10.65</v>
       </c>
-      <c r="I3" s="81" t="n">
+      <c r="I3" s="91" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="J3" s="81" t="n">
+      <c r="J3" s="91" t="n">
         <v>10.77</v>
       </c>
-      <c r="K3" s="81" t="n">
+      <c r="K3" s="91" t="n">
         <v>0.19</v>
       </c>
-      <c r="L3" s="81" t="n">
+      <c r="L3" s="91" t="n">
         <v>0.395</v>
       </c>
-      <c r="M3" s="81" t="n">
+      <c r="M3" s="91" t="n">
         <v>0.54</v>
       </c>
-      <c r="N3" s="81" t="n">
+      <c r="N3" s="91" t="n">
         <v>0.54</v>
       </c>
-      <c r="O3" s="81" t="n">
+      <c r="O3" s="91" t="n">
         <v>0.54</v>
       </c>
       <c r="P3" s="27" t="n"/>
@@ -5945,52 +5981,52 @@
       <c r="R3" s="27" t="n"/>
       <c r="S3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="29" t="inlineStr">
         <is>
           <t>ratevol</t>
         </is>
       </c>
-      <c r="B4" s="81" t="n">
+      <c r="B4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="81" t="n">
+      <c r="C4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="81" t="n">
+      <c r="D4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="E4" s="82" t="n">
+      <c r="E4" s="92" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="83" t="n">
+      <c r="F4" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="81" t="n">
+      <c r="G4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="H4" s="81" t="n">
+      <c r="H4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="81" t="n">
+      <c r="I4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="81" t="n">
+      <c r="J4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="K4" s="81" t="n">
+      <c r="K4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="L4" s="81" t="n">
+      <c r="L4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="M4" s="81" t="n">
+      <c r="M4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N4" s="81" t="n">
+      <c r="N4" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="O4" s="81" t="n">
+      <c r="O4" s="91" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="27" t="n"/>
@@ -5998,52 +6034,52 @@
       <c r="R4" s="27" t="n"/>
       <c r="S4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="29" t="inlineStr">
         <is>
           <t>addon</t>
         </is>
       </c>
-      <c r="B5" s="81" t="n">
+      <c r="B5" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="C5" s="81" t="n">
+      <c r="C5" s="91" t="n">
         <v>-0.25</v>
       </c>
-      <c r="D5" s="81" t="n">
+      <c r="D5" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="E5" s="82" t="n">
+      <c r="E5" s="92" t="n">
         <v>0.6</v>
       </c>
-      <c r="F5" s="83" t="n">
+      <c r="F5" s="93" t="n">
         <v>0.7</v>
       </c>
-      <c r="G5" s="81" t="n">
+      <c r="G5" s="91" t="n">
         <v>0.6</v>
       </c>
-      <c r="H5" s="81" t="n">
+      <c r="H5" s="91" t="n">
         <v>1.1</v>
       </c>
-      <c r="I5" s="81" t="n">
+      <c r="I5" s="91" t="n">
         <v>0.8</v>
       </c>
-      <c r="J5" s="81" t="n">
+      <c r="J5" s="91" t="n">
         <v>1.2</v>
       </c>
-      <c r="K5" s="81" t="n">
+      <c r="K5" s="91" t="n">
         <v>1.5</v>
       </c>
-      <c r="L5" s="81" t="n">
+      <c r="L5" s="91" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M5" s="81" t="n">
+      <c r="M5" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N5" s="81" t="n">
+      <c r="N5" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="O5" s="81" t="n">
+      <c r="O5" s="91" t="n">
         <v>0</v>
       </c>
       <c r="P5" s="27" t="n"/>
@@ -6051,52 +6087,52 @@
       <c r="R5" s="27" t="n"/>
       <c r="S5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="29" t="inlineStr">
         <is>
           <t>MR</t>
         </is>
       </c>
-      <c r="B6" s="81" t="n">
+      <c r="B6" s="91" t="n">
         <v>4.5</v>
       </c>
-      <c r="C6" s="81" t="n">
+      <c r="C6" s="91" t="n">
         <v>3.5</v>
       </c>
-      <c r="D6" s="81" t="n">
+      <c r="D6" s="91" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="82" t="n">
+      <c r="E6" s="92" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="83" t="n">
+      <c r="F6" s="93" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="81" t="n">
+      <c r="G6" s="91" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="81" t="n">
+      <c r="H6" s="91" t="n">
         <v>6.5</v>
       </c>
-      <c r="I6" s="81" t="n">
+      <c r="I6" s="91" t="n">
         <v>6</v>
       </c>
-      <c r="J6" s="81" t="n">
+      <c r="J6" s="91" t="n">
         <v>6.5</v>
       </c>
-      <c r="K6" s="81" t="n">
+      <c r="K6" s="91" t="n">
         <v>5.5</v>
       </c>
-      <c r="L6" s="81" t="n">
+      <c r="L6" s="91" t="n">
         <v>5</v>
       </c>
-      <c r="M6" s="81" t="n">
+      <c r="M6" s="91" t="n">
         <v>4</v>
       </c>
-      <c r="N6" s="81" t="n">
+      <c r="N6" s="91" t="n">
         <v>4</v>
       </c>
-      <c r="O6" s="81" t="n">
+      <c r="O6" s="91" t="n">
         <v>4</v>
       </c>
       <c r="P6" s="27" t="n"/>
@@ -6104,52 +6140,52 @@
       <c r="R6" s="27" t="n"/>
       <c r="S6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="29" t="inlineStr">
         <is>
           <t>rate corr</t>
         </is>
       </c>
-      <c r="B7" s="81" t="n">
+      <c r="B7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="C7" s="81" t="n">
+      <c r="C7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="81" t="n">
+      <c r="D7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="82" t="n">
+      <c r="E7" s="92" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="83" t="n">
+      <c r="F7" s="93" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="81" t="n">
+      <c r="G7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="81" t="n">
+      <c r="H7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="81" t="n">
+      <c r="I7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="81" t="n">
+      <c r="J7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="K7" s="81" t="n">
+      <c r="K7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="L7" s="81" t="n">
+      <c r="L7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="M7" s="81" t="n">
+      <c r="M7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="N7" s="81" t="n">
+      <c r="N7" s="91" t="n">
         <v>0</v>
       </c>
-      <c r="O7" s="81" t="n">
+      <c r="O7" s="91" t="n">
         <v>0</v>
       </c>
       <c r="P7" s="27" t="n"/>
@@ -6157,52 +6193,52 @@
       <c r="R7" s="27" t="n"/>
       <c r="S7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="29" t="inlineStr">
         <is>
           <t>short decay</t>
         </is>
       </c>
-      <c r="B8" s="81" t="n">
+      <c r="B8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="C8" s="81" t="n">
+      <c r="C8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="D8" s="81" t="n">
+      <c r="D8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="E8" s="82" t="n">
+      <c r="E8" s="92" t="n">
         <v>50</v>
       </c>
-      <c r="F8" s="83" t="n">
+      <c r="F8" s="93" t="n">
         <v>50</v>
       </c>
-      <c r="G8" s="81" t="n">
+      <c r="G8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="H8" s="81" t="n">
+      <c r="H8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="I8" s="81" t="n">
+      <c r="I8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="J8" s="81" t="n">
+      <c r="J8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="K8" s="81" t="n">
+      <c r="K8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="L8" s="81" t="n">
+      <c r="L8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="M8" s="81" t="n">
+      <c r="M8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="N8" s="81" t="n">
+      <c r="N8" s="91" t="n">
         <v>50</v>
       </c>
-      <c r="O8" s="81" t="n">
+      <c r="O8" s="91" t="n">
         <v>50</v>
       </c>
       <c r="P8" s="27" t="n"/>
@@ -6210,119 +6246,59 @@
       <c r="R8" s="27" t="n"/>
       <c r="S8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
-      <c r="A9" s="29" t="inlineStr">
-        <is>
-          <t>02/02/2024 00:00</t>
-        </is>
-      </c>
-      <c r="B9" s="81" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G9" s="81" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H9" s="81" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I9" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="J9" s="81" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K9" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="81" t="n">
-        <v>0</v>
-      </c>
+    <row r="9" ht="13.65" customHeight="1" s="102">
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>anchor</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="94" t="n"/>
+      <c r="F9" s="95" t="n"/>
+      <c r="G9" s="27" t="n"/>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="27" t="n"/>
+      <c r="J9" s="27" t="n"/>
+      <c r="K9" s="27" t="n"/>
+      <c r="L9" s="27" t="n"/>
+      <c r="M9" s="27" t="n"/>
+      <c r="N9" s="27" t="n"/>
+      <c r="O9" s="27" t="n"/>
       <c r="P9" s="27" t="n"/>
       <c r="Q9" s="27" t="n"/>
       <c r="R9" s="27" t="n"/>
       <c r="S9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
-      <c r="A10" s="29" t="inlineStr">
-        <is>
-          <t>02/02/2024 10:00</t>
-        </is>
-      </c>
-      <c r="B10" s="81" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="G10" s="81" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="H10" s="81" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="I10" s="81" t="n">
-        <v>6</v>
-      </c>
-      <c r="J10" s="81" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="K10" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="81" t="n">
-        <v>0</v>
-      </c>
+    <row r="10" ht="13.65" customHeight="1" s="102">
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="94" t="n"/>
+      <c r="F10" s="95" t="n"/>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="27" t="n"/>
+      <c r="J10" s="27" t="n"/>
+      <c r="K10" s="27" t="n"/>
+      <c r="L10" s="27" t="n"/>
+      <c r="M10" s="27" t="n"/>
+      <c r="N10" s="27" t="n"/>
+      <c r="O10" s="27" t="n"/>
       <c r="P10" s="27" t="n"/>
       <c r="Q10" s="27" t="n"/>
       <c r="R10" s="27" t="n"/>
       <c r="S10" s="27" t="n"/>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="27" t="n"/>
       <c r="B11" s="27" t="n"/>
       <c r="C11" s="27" t="n"/>
       <c r="D11" s="27" t="n"/>
-      <c r="E11" s="84" t="n"/>
-      <c r="F11" s="85" t="n"/>
+      <c r="E11" s="116" t="n"/>
+      <c r="F11" s="95" t="n"/>
       <c r="G11" s="27" t="n"/>
       <c r="H11" s="27" t="n"/>
       <c r="I11" s="27" t="n"/>
@@ -6337,13 +6313,13 @@
       <c r="R11" s="27" t="n"/>
       <c r="S11" s="27" t="n"/>
     </row>
-    <row r="12" ht="13.65" customHeight="1" s="93">
+    <row r="12" ht="13.65" customHeight="1" s="102">
       <c r="A12" s="27" t="n"/>
       <c r="B12" s="27" t="n"/>
       <c r="C12" s="27" t="n"/>
       <c r="D12" s="27" t="n"/>
-      <c r="E12" s="84" t="n"/>
-      <c r="F12" s="85" t="n"/>
+      <c r="E12" s="94" t="n"/>
+      <c r="F12" s="95" t="n"/>
       <c r="G12" s="27" t="n"/>
       <c r="H12" s="27" t="n"/>
       <c r="I12" s="27" t="n"/>
@@ -6358,13 +6334,13 @@
       <c r="R12" s="27" t="n"/>
       <c r="S12" s="27" t="n"/>
     </row>
-    <row r="13" ht="13.65" customHeight="1" s="93">
+    <row r="13" ht="13.65" customHeight="1" s="102">
       <c r="A13" s="27" t="n"/>
       <c r="B13" s="27" t="n"/>
       <c r="C13" s="27" t="n"/>
       <c r="D13" s="27" t="n"/>
-      <c r="E13" s="109" t="n"/>
-      <c r="F13" s="85" t="n"/>
+      <c r="E13" s="94" t="n"/>
+      <c r="F13" s="95" t="n"/>
       <c r="G13" s="27" t="n"/>
       <c r="H13" s="27" t="n"/>
       <c r="I13" s="27" t="n"/>
@@ -6379,13 +6355,13 @@
       <c r="R13" s="27" t="n"/>
       <c r="S13" s="27" t="n"/>
     </row>
-    <row r="14" ht="13.65" customHeight="1" s="93">
+    <row r="14" ht="13.65" customHeight="1" s="102">
       <c r="A14" s="27" t="n"/>
       <c r="B14" s="27" t="n"/>
       <c r="C14" s="27" t="n"/>
       <c r="D14" s="27" t="n"/>
-      <c r="E14" s="84" t="n"/>
-      <c r="F14" s="85" t="n"/>
+      <c r="E14" s="94" t="n"/>
+      <c r="F14" s="95" t="n"/>
       <c r="G14" s="27" t="n"/>
       <c r="H14" s="27" t="n"/>
       <c r="I14" s="27" t="n"/>
@@ -6398,15 +6374,15 @@
       <c r="P14" s="27" t="n"/>
       <c r="Q14" s="27" t="n"/>
       <c r="R14" s="27" t="n"/>
-      <c r="S14" s="27" t="n"/>
-    </row>
-    <row r="15" ht="13.65" customHeight="1" s="93">
+      <c r="S14" s="97" t="n"/>
+    </row>
+    <row r="15" ht="13.65" customHeight="1" s="102">
       <c r="A15" s="27" t="n"/>
       <c r="B15" s="27" t="n"/>
       <c r="C15" s="27" t="n"/>
       <c r="D15" s="27" t="n"/>
-      <c r="E15" s="84" t="n"/>
-      <c r="F15" s="85" t="n"/>
+      <c r="E15" s="94" t="n"/>
+      <c r="F15" s="95" t="n"/>
       <c r="G15" s="27" t="n"/>
       <c r="H15" s="27" t="n"/>
       <c r="I15" s="27" t="n"/>
@@ -6416,18 +6392,18 @@
       <c r="M15" s="27" t="n"/>
       <c r="N15" s="27" t="n"/>
       <c r="O15" s="27" t="n"/>
-      <c r="P15" s="27" t="n"/>
+      <c r="P15" s="111" t="n"/>
       <c r="Q15" s="27" t="n"/>
       <c r="R15" s="27" t="n"/>
       <c r="S15" s="27" t="n"/>
     </row>
-    <row r="16" ht="13.65" customHeight="1" s="93">
+    <row r="16" ht="13.65" customHeight="1" s="102">
       <c r="A16" s="27" t="n"/>
       <c r="B16" s="27" t="n"/>
       <c r="C16" s="27" t="n"/>
       <c r="D16" s="27" t="n"/>
-      <c r="E16" s="84" t="n"/>
-      <c r="F16" s="85" t="n"/>
+      <c r="E16" s="94" t="n"/>
+      <c r="F16" s="95" t="n"/>
       <c r="G16" s="27" t="n"/>
       <c r="H16" s="27" t="n"/>
       <c r="I16" s="27" t="n"/>
@@ -6437,18 +6413,18 @@
       <c r="M16" s="27" t="n"/>
       <c r="N16" s="27" t="n"/>
       <c r="O16" s="27" t="n"/>
-      <c r="P16" s="27" t="n"/>
+      <c r="P16" s="111" t="n"/>
       <c r="Q16" s="27" t="n"/>
       <c r="R16" s="27" t="n"/>
-      <c r="S16" s="87" t="n"/>
-    </row>
-    <row r="17" ht="13.65" customHeight="1" s="93">
+      <c r="S16" s="27" t="n"/>
+    </row>
+    <row r="17" ht="13.65" customHeight="1" s="102">
       <c r="A17" s="27" t="n"/>
       <c r="B17" s="27" t="n"/>
       <c r="C17" s="27" t="n"/>
       <c r="D17" s="27" t="n"/>
-      <c r="E17" s="84" t="n"/>
-      <c r="F17" s="85" t="n"/>
+      <c r="E17" s="94" t="n"/>
+      <c r="F17" s="95" t="n"/>
       <c r="G17" s="27" t="n"/>
       <c r="H17" s="27" t="n"/>
       <c r="I17" s="27" t="n"/>
@@ -6458,18 +6434,18 @@
       <c r="M17" s="27" t="n"/>
       <c r="N17" s="27" t="n"/>
       <c r="O17" s="27" t="n"/>
-      <c r="P17" s="104" t="n"/>
+      <c r="P17" s="111" t="n"/>
       <c r="Q17" s="27" t="n"/>
       <c r="R17" s="27" t="n"/>
       <c r="S17" s="27" t="n"/>
     </row>
-    <row r="18" ht="13.65" customHeight="1" s="93">
+    <row r="18" ht="13.65" customHeight="1" s="102">
       <c r="A18" s="27" t="n"/>
       <c r="B18" s="27" t="n"/>
       <c r="C18" s="27" t="n"/>
       <c r="D18" s="27" t="n"/>
-      <c r="E18" s="84" t="n"/>
-      <c r="F18" s="85" t="n"/>
+      <c r="E18" s="116" t="n"/>
+      <c r="F18" s="95" t="n"/>
       <c r="G18" s="27" t="n"/>
       <c r="H18" s="27" t="n"/>
       <c r="I18" s="27" t="n"/>
@@ -6479,18 +6455,18 @@
       <c r="M18" s="27" t="n"/>
       <c r="N18" s="27" t="n"/>
       <c r="O18" s="27" t="n"/>
-      <c r="P18" s="104" t="n"/>
+      <c r="P18" s="27" t="n"/>
       <c r="Q18" s="27" t="n"/>
       <c r="R18" s="27" t="n"/>
       <c r="S18" s="27" t="n"/>
     </row>
-    <row r="19" ht="13.65" customHeight="1" s="93">
+    <row r="19" ht="13.65" customHeight="1" s="102">
       <c r="A19" s="27" t="n"/>
       <c r="B19" s="27" t="n"/>
       <c r="C19" s="27" t="n"/>
       <c r="D19" s="27" t="n"/>
-      <c r="E19" s="84" t="n"/>
-      <c r="F19" s="85" t="n"/>
+      <c r="E19" s="116" t="n"/>
+      <c r="F19" s="95" t="n"/>
       <c r="G19" s="27" t="n"/>
       <c r="H19" s="27" t="n"/>
       <c r="I19" s="27" t="n"/>
@@ -6500,18 +6476,18 @@
       <c r="M19" s="27" t="n"/>
       <c r="N19" s="27" t="n"/>
       <c r="O19" s="27" t="n"/>
-      <c r="P19" s="104" t="n"/>
+      <c r="P19" s="27" t="n"/>
       <c r="Q19" s="27" t="n"/>
       <c r="R19" s="27" t="n"/>
       <c r="S19" s="27" t="n"/>
     </row>
-    <row r="20" ht="13.65" customHeight="1" s="93">
+    <row r="20" ht="13.65" customHeight="1" s="102">
       <c r="A20" s="27" t="n"/>
       <c r="B20" s="27" t="n"/>
       <c r="C20" s="27" t="n"/>
       <c r="D20" s="27" t="n"/>
-      <c r="E20" s="109" t="n"/>
-      <c r="F20" s="85" t="n"/>
+      <c r="E20" s="116" t="n"/>
+      <c r="F20" s="95" t="n"/>
       <c r="G20" s="27" t="n"/>
       <c r="H20" s="27" t="n"/>
       <c r="I20" s="27" t="n"/>
@@ -6526,16 +6502,16 @@
       <c r="R20" s="27" t="n"/>
       <c r="S20" s="27" t="n"/>
     </row>
-    <row r="21" ht="13.65" customHeight="1" s="93">
+    <row r="21" ht="13.65" customHeight="1" s="102">
       <c r="A21" s="27" t="n"/>
       <c r="B21" s="27" t="n"/>
       <c r="C21" s="27" t="n"/>
       <c r="D21" s="27" t="n"/>
-      <c r="E21" s="109" t="n"/>
-      <c r="F21" s="85" t="n"/>
+      <c r="E21" s="116" t="n"/>
+      <c r="F21" s="95" t="n"/>
       <c r="G21" s="27" t="n"/>
       <c r="H21" s="27" t="n"/>
-      <c r="I21" s="27" t="n"/>
+      <c r="I21" s="111" t="n"/>
       <c r="J21" s="27" t="n"/>
       <c r="K21" s="27" t="n"/>
       <c r="L21" s="27" t="n"/>
@@ -6547,13 +6523,13 @@
       <c r="R21" s="27" t="n"/>
       <c r="S21" s="27" t="n"/>
     </row>
-    <row r="22" ht="13.65" customHeight="1" s="93">
+    <row r="22" ht="13.65" customHeight="1" s="102">
       <c r="A22" s="27" t="n"/>
       <c r="B22" s="27" t="n"/>
       <c r="C22" s="27" t="n"/>
       <c r="D22" s="27" t="n"/>
-      <c r="E22" s="109" t="n"/>
-      <c r="F22" s="85" t="n"/>
+      <c r="E22" s="94" t="n"/>
+      <c r="F22" s="95" t="n"/>
       <c r="G22" s="27" t="n"/>
       <c r="H22" s="27" t="n"/>
       <c r="I22" s="27" t="n"/>
@@ -6568,20 +6544,20 @@
       <c r="R22" s="27" t="n"/>
       <c r="S22" s="27" t="n"/>
     </row>
-    <row r="23" ht="13.65" customHeight="1" s="93">
+    <row r="23" ht="13.65" customHeight="1" s="102">
       <c r="A23" s="27" t="n"/>
       <c r="B23" s="27" t="n"/>
       <c r="C23" s="27" t="n"/>
       <c r="D23" s="27" t="n"/>
-      <c r="E23" s="109" t="n"/>
-      <c r="F23" s="85" t="n"/>
+      <c r="E23" s="94" t="n"/>
+      <c r="F23" s="95" t="n"/>
       <c r="G23" s="27" t="n"/>
       <c r="H23" s="27" t="n"/>
-      <c r="I23" s="104" t="n"/>
+      <c r="I23" s="27" t="n"/>
       <c r="J23" s="27" t="n"/>
       <c r="K23" s="27" t="n"/>
       <c r="L23" s="27" t="n"/>
-      <c r="M23" s="27" t="n"/>
+      <c r="M23" s="111" t="n"/>
       <c r="N23" s="27" t="n"/>
       <c r="O23" s="27" t="n"/>
       <c r="P23" s="27" t="n"/>
@@ -6589,20 +6565,20 @@
       <c r="R23" s="27" t="n"/>
       <c r="S23" s="27" t="n"/>
     </row>
-    <row r="24" ht="13.65" customHeight="1" s="93">
+    <row r="24" ht="13.65" customHeight="1" s="102">
       <c r="A24" s="27" t="n"/>
       <c r="B24" s="27" t="n"/>
       <c r="C24" s="27" t="n"/>
       <c r="D24" s="27" t="n"/>
-      <c r="E24" s="84" t="n"/>
-      <c r="F24" s="85" t="n"/>
+      <c r="E24" s="94" t="n"/>
+      <c r="F24" s="95" t="n"/>
       <c r="G24" s="27" t="n"/>
       <c r="H24" s="27" t="n"/>
       <c r="I24" s="27" t="n"/>
       <c r="J24" s="27" t="n"/>
       <c r="K24" s="27" t="n"/>
       <c r="L24" s="27" t="n"/>
-      <c r="M24" s="27" t="n"/>
+      <c r="M24" s="111" t="n"/>
       <c r="N24" s="27" t="n"/>
       <c r="O24" s="27" t="n"/>
       <c r="P24" s="27" t="n"/>
@@ -6610,48 +6586,8 @@
       <c r="R24" s="27" t="n"/>
       <c r="S24" s="27" t="n"/>
     </row>
-    <row r="25" ht="13.65" customHeight="1" s="93">
-      <c r="A25" s="27" t="n"/>
-      <c r="B25" s="27" t="n"/>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="84" t="n"/>
-      <c r="F25" s="85" t="n"/>
-      <c r="G25" s="27" t="n"/>
-      <c r="H25" s="27" t="n"/>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="27" t="n"/>
-      <c r="M25" s="104" t="n"/>
-      <c r="N25" s="27" t="n"/>
-      <c r="O25" s="27" t="n"/>
-      <c r="P25" s="27" t="n"/>
-      <c r="Q25" s="27" t="n"/>
-      <c r="R25" s="27" t="n"/>
-      <c r="S25" s="27" t="n"/>
-    </row>
-    <row r="26" ht="13.65" customHeight="1" s="93">
-      <c r="A26" s="27" t="n"/>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="84" t="n"/>
-      <c r="F26" s="85" t="n"/>
-      <c r="G26" s="27" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="27" t="n"/>
-      <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="27" t="n"/>
-      <c r="M26" s="104" t="n"/>
-      <c r="N26" s="27" t="n"/>
-      <c r="O26" s="27" t="n"/>
-      <c r="P26" s="27" t="n"/>
-      <c r="Q26" s="27" t="n"/>
-      <c r="R26" s="27" t="n"/>
-      <c r="S26" s="27" t="n"/>
-    </row>
+    <row r="25" ht="13.65" customHeight="1" s="102"/>
+    <row r="26" ht="13.65" customHeight="1" s="102"/>
   </sheetData>
   <pageMargins left="0.7875" right="0.7875" top="1.05278" bottom="1.05278" header="0.7875" footer="0.7875"/>
   <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
@@ -6670,1032 +6606,244 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P40"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
+  <dimension ref="A1:W3"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.8333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="15.1719" customWidth="1" style="90" min="1" max="1"/>
-    <col width="11.3516" customWidth="1" style="90" min="2" max="2"/>
-    <col width="12.8516" customWidth="1" style="90" min="3" max="3"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="4" max="5"/>
-    <col width="11.5" customWidth="1" style="90" min="6" max="6"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="7" max="12"/>
-    <col width="12.8516" customWidth="1" style="90" min="13" max="13"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="14" max="16"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="17" max="16384"/>
+    <col width="15.1719" customWidth="1" style="99" min="1" max="1"/>
+    <col width="10.8516" customWidth="1" style="99" min="2" max="22"/>
+    <col width="11.8516" customWidth="1" style="99" min="23" max="27"/>
+    <col width="11.8516" customWidth="1" style="99" min="28" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
-      <c r="A1" s="29" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="29" t="inlineStr">
-        <is>
-          <t>daily</t>
-        </is>
-      </c>
-      <c r="C1" s="29" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-      <c r="F1" s="27" t="n"/>
-      <c r="G1" s="27" t="n"/>
-      <c r="H1" s="27" t="n"/>
-      <c r="I1" s="27" t="n"/>
-      <c r="J1" s="27" t="n"/>
-      <c r="K1" s="27" t="n"/>
-      <c r="L1" s="27" t="n"/>
-      <c r="M1" s="27" t="n"/>
-      <c r="N1" s="27" t="n"/>
-      <c r="O1" s="27" t="n"/>
-      <c r="P1" s="27" t="n"/>
-    </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
-      <c r="A2" s="110" t="n">
-        <v>44209</v>
-      </c>
-      <c r="B2" s="104" t="n">
-        <v>0</v>
-      </c>
-      <c r="C2" s="104" t="n">
-        <v>1500000</v>
-      </c>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
-      <c r="F2" s="27" t="n"/>
-      <c r="G2" s="27" t="n"/>
-      <c r="H2" s="27" t="n"/>
-      <c r="I2" s="27" t="n"/>
-      <c r="J2" s="27" t="n"/>
-      <c r="K2" s="27" t="n"/>
-      <c r="L2" s="27" t="n"/>
-      <c r="M2" s="27" t="n"/>
-      <c r="N2" s="27" t="n"/>
-      <c r="O2" s="27" t="n"/>
-      <c r="P2" s="27" t="n"/>
-    </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
-      <c r="A3" s="110" t="n">
-        <v>44210</v>
-      </c>
-      <c r="B3" s="104" t="n">
-        <v>1788</v>
-      </c>
-      <c r="C3" s="104">
-        <f t="array" ref="C3">C2+B3</f>
-        <v>1501788.0</v>
-      </c>
-      <c r="D3" s="27" t="n"/>
-      <c r="E3" s="27" t="n"/>
-      <c r="F3" s="27" t="n"/>
-      <c r="G3" s="27" t="n"/>
-      <c r="H3" s="27" t="n"/>
-      <c r="I3" s="27" t="n"/>
-      <c r="J3" s="27" t="n"/>
-      <c r="K3" s="27" t="n"/>
-      <c r="L3" s="27" t="n"/>
-      <c r="M3" s="27" t="n"/>
-      <c r="N3" s="27" t="n"/>
-      <c r="O3" s="27" t="n"/>
-      <c r="P3" s="27" t="n"/>
-    </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
-      <c r="A4" s="110" t="n">
-        <v>44211</v>
-      </c>
-      <c r="B4" s="104" t="n">
-        <v>88251</v>
-      </c>
-      <c r="C4" s="104">
-        <f t="array" ref="C4">C3+B4</f>
-        <v>1590039.0</v>
-      </c>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="27" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="27" t="n"/>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="27" t="n"/>
-      <c r="M4" s="27" t="n"/>
-      <c r="N4" s="27" t="n"/>
-      <c r="O4" s="27" t="n"/>
-      <c r="P4" s="27" t="n"/>
-    </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
-      <c r="A5" s="110" t="n">
-        <v>44214</v>
-      </c>
-      <c r="B5" s="104">
-        <f t="array" ref="B5">332875</f>
-        <v>332875.0</v>
-      </c>
-      <c r="C5" s="104">
-        <f t="array" ref="C5">C4+B5</f>
-        <v>1922914.0</v>
-      </c>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="81" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="27" t="n"/>
-      <c r="K5" s="27" t="n"/>
-      <c r="L5" s="27" t="n"/>
-      <c r="M5" s="27" t="n"/>
-      <c r="N5" s="27" t="n"/>
-      <c r="O5" s="27" t="n"/>
-      <c r="P5" s="27" t="n"/>
-    </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
-      <c r="A6" s="110" t="n">
-        <v>44215</v>
-      </c>
-      <c r="B6" s="104" t="n">
-        <v>5327</v>
-      </c>
-      <c r="C6" s="104">
-        <f t="array" ref="C6">C5+B6</f>
-        <v>1928241.0</v>
-      </c>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="81" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="27" t="n"/>
-      <c r="J6" s="27" t="n"/>
-      <c r="K6" s="27" t="n"/>
-      <c r="L6" s="27" t="n"/>
-      <c r="M6" s="27" t="n"/>
-      <c r="N6" s="104" t="n"/>
-      <c r="O6" s="27" t="n"/>
-      <c r="P6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
-      <c r="A7" s="110" t="n">
-        <v>44216</v>
-      </c>
-      <c r="B7" s="104" t="n">
-        <v>289118</v>
-      </c>
-      <c r="C7" s="104">
-        <f t="array" ref="C7">C6+B7</f>
-        <v>2217359.0</v>
-      </c>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
-      <c r="L7" s="27" t="n"/>
-      <c r="M7" s="27" t="n"/>
-      <c r="N7" s="104" t="n"/>
-      <c r="O7" s="27" t="n"/>
-      <c r="P7" s="27" t="n"/>
-    </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
-      <c r="A8" s="110" t="n">
-        <v>44217</v>
-      </c>
-      <c r="B8" s="104" t="n">
-        <v>240028</v>
-      </c>
-      <c r="C8" s="104">
-        <f t="array" ref="C8">C7+B8</f>
-        <v>2457387.0</v>
-      </c>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="27" t="n"/>
-      <c r="M8" s="27" t="n"/>
-      <c r="N8" s="104" t="n"/>
-      <c r="O8" s="27" t="n"/>
-      <c r="P8" s="27" t="n"/>
-    </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
-      <c r="A9" s="110" t="n">
-        <v>44218</v>
-      </c>
-      <c r="B9" s="104" t="n">
-        <v>684479</v>
-      </c>
-      <c r="C9" s="104">
-        <f t="array" ref="C9">C8+B9</f>
-        <v>3141866.0</v>
-      </c>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="27" t="n"/>
-      <c r="J9" s="27" t="n"/>
-      <c r="K9" s="27" t="n"/>
-      <c r="L9" s="27" t="n"/>
-      <c r="M9" s="27" t="n"/>
-      <c r="N9" s="27" t="n"/>
-      <c r="O9" s="27" t="n"/>
-      <c r="P9" s="27" t="n"/>
-    </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
-      <c r="A10" s="110" t="n">
-        <v>44221</v>
-      </c>
-      <c r="B10" s="104" t="n">
-        <v>60818</v>
-      </c>
-      <c r="C10" s="104">
-        <f t="array" ref="C10">C9+B10</f>
-        <v>3202684.0</v>
-      </c>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="27" t="n"/>
-      <c r="M10" s="27" t="n"/>
-      <c r="N10" s="27" t="n"/>
-      <c r="O10" s="27" t="n"/>
-      <c r="P10" s="27" t="n"/>
-    </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
-      <c r="A11" s="110" t="n">
-        <v>44222</v>
-      </c>
-      <c r="B11" s="104" t="n">
-        <v>27441</v>
-      </c>
-      <c r="C11" s="104">
-        <f t="array" ref="C11">C10+B11</f>
-        <v>3230125.0</v>
-      </c>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
-      <c r="M11" s="27" t="n"/>
-      <c r="N11" s="27" t="n"/>
-      <c r="O11" s="27" t="n"/>
-      <c r="P11" s="27" t="n"/>
-    </row>
-    <row r="12" ht="13.65" customHeight="1" s="93">
-      <c r="A12" s="110" t="n">
-        <v>44223</v>
-      </c>
-      <c r="B12" s="104" t="n">
-        <v>2993</v>
-      </c>
-      <c r="C12" s="104">
-        <f t="array" ref="C12">C11+B12</f>
-        <v>3233118.0</v>
-      </c>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="27" t="n"/>
-      <c r="M12" s="27" t="n"/>
-      <c r="N12" s="27" t="n"/>
-      <c r="O12" s="27" t="n"/>
-      <c r="P12" s="27" t="n"/>
-    </row>
-    <row r="13" ht="13.65" customHeight="1" s="93">
-      <c r="A13" s="110" t="n">
-        <v>44224</v>
-      </c>
-      <c r="B13" s="104" t="n">
-        <v>27335</v>
-      </c>
-      <c r="C13" s="104">
-        <f t="array" ref="C13">C12+B13</f>
-        <v>3260453.0</v>
-      </c>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
-      <c r="M13" s="27" t="n"/>
-      <c r="N13" s="104" t="n"/>
-      <c r="O13" s="27" t="n"/>
-      <c r="P13" s="27" t="n"/>
-    </row>
-    <row r="14" ht="13.65" customHeight="1" s="93">
-      <c r="A14" s="110" t="n">
-        <v>44225</v>
-      </c>
-      <c r="B14" s="104" t="n">
-        <v>393956</v>
-      </c>
-      <c r="C14" s="104">
-        <f t="array" ref="C14">C13+B14</f>
-        <v>3654409.0</v>
-      </c>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
-      <c r="M14" s="104" t="n"/>
-      <c r="N14" s="27" t="n"/>
-      <c r="O14" s="27" t="n"/>
-      <c r="P14" s="27" t="n"/>
-    </row>
-    <row r="15" ht="13.65" customHeight="1" s="93">
-      <c r="A15" s="110" t="n">
-        <v>44228</v>
-      </c>
-      <c r="B15" s="104" t="n">
-        <v>14926</v>
-      </c>
-      <c r="C15" s="104">
-        <f t="array" ref="C15">C14+B15</f>
-        <v>3669335.0</v>
-      </c>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="27" t="n"/>
-      <c r="K15" s="27" t="n"/>
-      <c r="L15" s="27" t="n"/>
-      <c r="M15" s="27" t="n"/>
-      <c r="N15" s="27" t="n"/>
-      <c r="O15" s="27" t="n"/>
-      <c r="P15" s="27" t="n"/>
-    </row>
-    <row r="16" ht="13.65" customHeight="1" s="93">
-      <c r="A16" s="110" t="n">
-        <v>44229</v>
-      </c>
-      <c r="B16" s="104" t="n">
-        <v>10778</v>
-      </c>
-      <c r="C16" s="104">
-        <f t="array" ref="C16">C15+B16</f>
-        <v>3680113.0</v>
-      </c>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="27" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="27" t="n"/>
-      <c r="M16" s="27" t="n"/>
-      <c r="N16" s="27" t="n"/>
-      <c r="O16" s="27" t="n"/>
-      <c r="P16" s="27" t="n"/>
-    </row>
-    <row r="17" ht="13.65" customHeight="1" s="93">
-      <c r="A17" s="110" t="n">
-        <v>44230</v>
-      </c>
-      <c r="B17" s="104" t="n">
-        <v>1277</v>
-      </c>
-      <c r="C17" s="104">
-        <f t="array" ref="C17">C16+B17</f>
-        <v>3681390.0</v>
-      </c>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="27" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="27" t="n"/>
-      <c r="L17" s="27" t="n"/>
-      <c r="M17" s="27" t="n"/>
-      <c r="N17" s="27" t="n"/>
-      <c r="O17" s="27" t="n"/>
-      <c r="P17" s="104" t="n"/>
-    </row>
-    <row r="18" ht="13.65" customHeight="1" s="93">
-      <c r="A18" s="110" t="n">
-        <v>44231</v>
-      </c>
-      <c r="B18" s="104" t="n">
-        <v>799207</v>
-      </c>
-      <c r="C18" s="104">
-        <f t="array" ref="C18">C17+B18</f>
-        <v>4480597.0</v>
-      </c>
-      <c r="D18" s="27" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="27" t="n"/>
-      <c r="J18" s="27" t="n"/>
-      <c r="K18" s="27" t="n"/>
-      <c r="L18" s="27" t="n"/>
-      <c r="M18" s="27" t="n"/>
-      <c r="N18" s="27" t="n"/>
-      <c r="O18" s="27" t="n"/>
-      <c r="P18" s="104" t="n"/>
-    </row>
-    <row r="19" ht="13.65" customHeight="1" s="93">
-      <c r="A19" s="110" t="n">
-        <v>44232</v>
-      </c>
-      <c r="B19" s="104" t="n">
-        <v>294861</v>
-      </c>
-      <c r="C19" s="104">
-        <f t="array" ref="C19">C18+B19</f>
-        <v>4775458.0</v>
-      </c>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="27" t="n"/>
-      <c r="I19" s="27" t="n"/>
-      <c r="J19" s="27" t="n"/>
-      <c r="K19" s="27" t="n"/>
-      <c r="L19" s="27" t="n"/>
-      <c r="M19" s="27" t="n"/>
-      <c r="N19" s="27" t="n"/>
-      <c r="O19" s="27" t="n"/>
-      <c r="P19" s="104" t="n"/>
-    </row>
-    <row r="20" ht="13.65" customHeight="1" s="93">
-      <c r="A20" s="110" t="n">
-        <v>44235</v>
-      </c>
-      <c r="B20" s="104" t="n">
-        <v>73054</v>
-      </c>
-      <c r="C20" s="104">
-        <f t="array" ref="C20">C19+B20</f>
-        <v>4848512.0</v>
-      </c>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="27" t="n"/>
-      <c r="M20" s="27" t="n"/>
-      <c r="N20" s="104" t="n"/>
-      <c r="O20" s="27" t="n"/>
-      <c r="P20" s="27" t="n"/>
-    </row>
-    <row r="21" ht="13.65" customHeight="1" s="93">
-      <c r="A21" s="110" t="n">
-        <v>44236</v>
-      </c>
-      <c r="B21" s="104" t="n">
-        <v>395464</v>
-      </c>
-      <c r="C21" s="104">
-        <f t="array" ref="C21">C20+B21</f>
-        <v>5243976.0</v>
-      </c>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="27" t="n"/>
-      <c r="I21" s="27" t="n"/>
-      <c r="J21" s="27" t="n"/>
-      <c r="K21" s="27" t="n"/>
-      <c r="L21" s="27" t="n"/>
-      <c r="M21" s="27" t="n"/>
-      <c r="N21" s="104" t="n"/>
-      <c r="O21" s="27" t="n"/>
-      <c r="P21" s="27" t="n"/>
-    </row>
-    <row r="22" ht="13.65" customHeight="1" s="93">
-      <c r="A22" s="110" t="n">
-        <v>44237</v>
-      </c>
-      <c r="B22" s="104" t="n">
-        <v>1023759</v>
-      </c>
-      <c r="C22" s="104">
-        <f t="array" ref="C22">C21+B22</f>
-        <v>6267735.0</v>
-      </c>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
-      <c r="H22" s="27" t="n"/>
-      <c r="I22" s="27" t="n"/>
-      <c r="J22" s="27" t="n"/>
-      <c r="K22" s="27" t="n"/>
-      <c r="L22" s="27" t="n"/>
-      <c r="M22" s="27" t="n"/>
-      <c r="N22" s="104" t="n"/>
-      <c r="O22" s="27" t="n"/>
-      <c r="P22" s="27" t="n"/>
-    </row>
-    <row r="23" ht="13.65" customHeight="1" s="93">
-      <c r="A23" s="110" t="n">
-        <v>44238</v>
-      </c>
-      <c r="B23" s="104" t="n">
-        <v>887</v>
-      </c>
-      <c r="C23" s="104">
-        <f t="array" ref="C23">C22+B23</f>
-        <v>6268622.0</v>
-      </c>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="104" t="n"/>
-      <c r="K23" s="27" t="n"/>
-      <c r="L23" s="27" t="n"/>
-      <c r="M23" s="27" t="n"/>
-      <c r="N23" s="104" t="n"/>
-      <c r="O23" s="27" t="n"/>
-      <c r="P23" s="27" t="n"/>
-    </row>
-    <row r="24" ht="13.65" customHeight="1" s="93">
-      <c r="A24" s="110" t="n">
-        <v>44245</v>
-      </c>
-      <c r="B24" s="104" t="n">
-        <v>135508</v>
-      </c>
-      <c r="C24" s="104">
-        <f t="array" ref="C24">C23+B24</f>
-        <v>6404130.0</v>
-      </c>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="27" t="n"/>
-      <c r="H24" s="27" t="n"/>
-      <c r="I24" s="27" t="n"/>
-      <c r="J24" s="27" t="n"/>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="27" t="n"/>
-      <c r="M24" s="27" t="n"/>
-      <c r="N24" s="27" t="n"/>
-      <c r="O24" s="27" t="n"/>
-      <c r="P24" s="27" t="n"/>
-    </row>
-    <row r="25" ht="13.65" customHeight="1" s="93">
-      <c r="A25" s="110" t="n">
-        <v>44246</v>
-      </c>
-      <c r="B25" s="104" t="n">
-        <v>547551</v>
-      </c>
-      <c r="C25" s="104">
-        <f t="array" ref="C25">C24+B25</f>
-        <v>6951681.0</v>
-      </c>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="27" t="n"/>
-      <c r="G25" s="27" t="n"/>
-      <c r="H25" s="27" t="n"/>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="27" t="n"/>
-      <c r="K25" s="27" t="n"/>
-      <c r="L25" s="104" t="n"/>
-      <c r="M25" s="27" t="n"/>
-      <c r="N25" s="27" t="n"/>
-      <c r="O25" s="27" t="n"/>
-      <c r="P25" s="27" t="n"/>
-    </row>
-    <row r="26" ht="13.65" customHeight="1" s="93">
-      <c r="A26" s="110" t="n">
-        <v>44247</v>
-      </c>
-      <c r="B26" s="104" t="n">
-        <v>142388</v>
-      </c>
-      <c r="C26" s="104">
-        <f t="array" ref="C26">C25+B26</f>
-        <v>7094069.0</v>
-      </c>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="27" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="27" t="n"/>
-      <c r="J26" s="27" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="104" t="n"/>
-      <c r="M26" s="27" t="n"/>
-      <c r="N26" s="27" t="n"/>
-      <c r="O26" s="27" t="n"/>
-      <c r="P26" s="27" t="n"/>
-    </row>
-    <row r="27" ht="13.65" customHeight="1" s="93">
-      <c r="A27" s="110" t="n">
-        <v>44250</v>
-      </c>
-      <c r="B27" s="104" t="n">
-        <v>7800</v>
-      </c>
-      <c r="C27" s="104">
-        <f t="array" ref="C27">C26+B27</f>
-        <v>7101869.0</v>
-      </c>
-      <c r="D27" s="27" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="27" t="n"/>
-      <c r="G27" s="27" t="n"/>
-      <c r="H27" s="27" t="n"/>
-      <c r="I27" s="27" t="n"/>
-      <c r="J27" s="27" t="n"/>
-      <c r="K27" s="27" t="n"/>
-      <c r="L27" s="27" t="n"/>
-      <c r="M27" s="27" t="n"/>
-      <c r="N27" s="27" t="n"/>
-      <c r="O27" s="27" t="n"/>
-      <c r="P27" s="27" t="n"/>
-    </row>
-    <row r="28" ht="13.65" customHeight="1" s="93">
-      <c r="A28" s="110" t="n">
-        <v>44251</v>
-      </c>
-      <c r="B28" s="104" t="n">
-        <v>15182</v>
-      </c>
-      <c r="C28" s="104">
-        <f t="array" ref="C28">C27+B28</f>
-        <v>7117051.0</v>
-      </c>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="27" t="n"/>
-      <c r="H28" s="27" t="n"/>
-      <c r="I28" s="27" t="n"/>
-      <c r="J28" s="27" t="n"/>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="27" t="n"/>
-      <c r="M28" s="27" t="n"/>
-      <c r="N28" s="27" t="n"/>
-      <c r="O28" s="27" t="n"/>
-      <c r="P28" s="27" t="n"/>
-    </row>
-    <row r="29" ht="13.65" customHeight="1" s="93">
-      <c r="A29" s="110" t="n">
-        <v>44252</v>
-      </c>
-      <c r="B29" s="104" t="n">
-        <v>72930</v>
-      </c>
-      <c r="C29" s="104">
-        <f t="array" ref="C29">C28+B29</f>
-        <v>7189981.0</v>
-      </c>
-      <c r="D29" s="27" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="27" t="n"/>
-      <c r="G29" s="27" t="n"/>
-      <c r="H29" s="27" t="n"/>
-      <c r="I29" s="27" t="n"/>
-      <c r="J29" s="27" t="n"/>
-      <c r="K29" s="27" t="n"/>
-      <c r="L29" s="27" t="n"/>
-      <c r="M29" s="27" t="n"/>
-      <c r="N29" s="27" t="n"/>
-      <c r="O29" s="27" t="n"/>
-      <c r="P29" s="27" t="n"/>
-    </row>
-    <row r="30" ht="13.65" customHeight="1" s="93">
-      <c r="A30" s="110" t="n">
-        <v>44253</v>
-      </c>
-      <c r="B30" s="104" t="n">
-        <v>355319</v>
-      </c>
-      <c r="C30" s="104">
-        <f t="array" ref="C30">C29+B30</f>
-        <v>7545300.0</v>
-      </c>
-      <c r="D30" s="27" t="n"/>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="27" t="n"/>
-      <c r="H30" s="27" t="n"/>
-      <c r="I30" s="27" t="n"/>
-      <c r="J30" s="27" t="n"/>
-      <c r="K30" s="27" t="n"/>
-      <c r="L30" s="27" t="n"/>
-      <c r="M30" s="27" t="n"/>
-      <c r="N30" s="27" t="n"/>
-      <c r="O30" s="27" t="n"/>
-      <c r="P30" s="27" t="n"/>
-    </row>
-    <row r="31" ht="13.65" customHeight="1" s="93">
-      <c r="A31" s="110" t="n">
-        <v>44256</v>
-      </c>
-      <c r="B31" s="104" t="n">
-        <v>53944</v>
-      </c>
-      <c r="C31" s="104">
-        <f t="array" ref="C31">C30+B31</f>
-        <v>7599244.0</v>
-      </c>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="27" t="n"/>
-      <c r="G31" s="27" t="n"/>
-      <c r="H31" s="27" t="n"/>
-      <c r="I31" s="27" t="n"/>
-      <c r="J31" s="27" t="n"/>
-      <c r="K31" s="27" t="n"/>
-      <c r="L31" s="27" t="n"/>
-      <c r="M31" s="27" t="n"/>
-      <c r="N31" s="27" t="n"/>
-      <c r="O31" s="27" t="n"/>
-      <c r="P31" s="27" t="n"/>
-    </row>
-    <row r="32" ht="13.65" customHeight="1" s="93">
-      <c r="A32" s="110" t="n">
-        <v>44257</v>
-      </c>
-      <c r="B32" s="104" t="n">
-        <v>82223</v>
-      </c>
-      <c r="C32" s="104">
-        <f t="array" ref="C32">C31+B32</f>
-        <v>7681467.0</v>
-      </c>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="27" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="27" t="n"/>
-      <c r="J32" s="27" t="n"/>
-      <c r="K32" s="27" t="n"/>
-      <c r="L32" s="27" t="n"/>
-      <c r="M32" s="27" t="n"/>
-      <c r="N32" s="27" t="n"/>
-      <c r="O32" s="27" t="n"/>
-      <c r="P32" s="27" t="n"/>
-    </row>
-    <row r="33" ht="13.65" customHeight="1" s="93">
-      <c r="A33" s="110" t="n">
-        <v>44258</v>
-      </c>
-      <c r="B33" s="104" t="n">
-        <v>223373</v>
-      </c>
-      <c r="C33" s="104">
-        <f t="array" ref="C33">C32+B33</f>
-        <v>7904840.0</v>
-      </c>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="27" t="n"/>
-      <c r="G33" s="27" t="n"/>
-      <c r="H33" s="27" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="27" t="n"/>
-      <c r="K33" s="27" t="n"/>
-      <c r="L33" s="27" t="n"/>
-      <c r="M33" s="27" t="n"/>
-      <c r="N33" s="27" t="n"/>
-      <c r="O33" s="27" t="n"/>
-      <c r="P33" s="27" t="n"/>
-    </row>
-    <row r="34" ht="13.65" customHeight="1" s="93">
-      <c r="A34" s="110" t="n">
-        <v>44259</v>
-      </c>
-      <c r="B34" s="104" t="n">
-        <v>29125</v>
-      </c>
-      <c r="C34" s="104">
-        <f t="array" ref="C34">C33+B34</f>
-        <v>7933965.0</v>
-      </c>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="27" t="n"/>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="27" t="n"/>
-      <c r="J34" s="27" t="n"/>
-      <c r="K34" s="27" t="n"/>
-      <c r="L34" s="27" t="n"/>
-      <c r="M34" s="27" t="n"/>
-      <c r="N34" s="27" t="n"/>
-      <c r="O34" s="27" t="n"/>
-      <c r="P34" s="27" t="n"/>
-    </row>
-    <row r="35" ht="13.65" customHeight="1" s="93">
-      <c r="A35" s="110" t="n">
-        <v>44260</v>
-      </c>
-      <c r="B35" s="104" t="n">
-        <v>143283</v>
-      </c>
-      <c r="C35" s="104">
-        <f t="array" ref="C35">C34+B35</f>
-        <v>8077248.0</v>
-      </c>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="27" t="n"/>
-      <c r="G35" s="27" t="n"/>
-      <c r="H35" s="27" t="n"/>
-      <c r="I35" s="27" t="n"/>
-      <c r="J35" s="27" t="n"/>
-      <c r="K35" s="27" t="n"/>
-      <c r="L35" s="27" t="n"/>
-      <c r="M35" s="27" t="n"/>
-      <c r="N35" s="27" t="n"/>
-      <c r="O35" s="27" t="n"/>
-      <c r="P35" s="27" t="n"/>
-    </row>
-    <row r="36" ht="13.65" customHeight="1" s="93">
-      <c r="A36" s="110" t="n">
-        <v>44263</v>
-      </c>
-      <c r="B36" s="104" t="n">
-        <v>207645</v>
-      </c>
-      <c r="C36" s="104">
-        <f t="array" ref="C36">C35+B36</f>
-        <v>8284893.0</v>
-      </c>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="27" t="n"/>
-      <c r="H36" s="27" t="n"/>
-      <c r="I36" s="27" t="n"/>
-      <c r="J36" s="27" t="n"/>
-      <c r="K36" s="27" t="n"/>
-      <c r="L36" s="27" t="n"/>
-      <c r="M36" s="27" t="n"/>
-      <c r="N36" s="27" t="n"/>
-      <c r="O36" s="27" t="n"/>
-      <c r="P36" s="27" t="n"/>
-    </row>
-    <row r="37" ht="13.65" customHeight="1" s="93">
-      <c r="A37" s="110" t="n">
-        <v>44264</v>
-      </c>
-      <c r="B37" s="104" t="n">
-        <v>217531</v>
-      </c>
-      <c r="C37" s="104">
-        <f t="array" ref="C37">C36+B37</f>
-        <v>8502424.0</v>
-      </c>
-      <c r="D37" s="27" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="27" t="n"/>
-      <c r="G37" s="27" t="n"/>
-      <c r="H37" s="27" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="27" t="n"/>
-      <c r="K37" s="27" t="n"/>
-      <c r="L37" s="27" t="n"/>
-      <c r="M37" s="27" t="n"/>
-      <c r="N37" s="27" t="n"/>
-      <c r="O37" s="27" t="n"/>
-      <c r="P37" s="27" t="n"/>
-    </row>
-    <row r="38" ht="13.65" customHeight="1" s="93">
-      <c r="A38" s="110" t="n">
-        <v>44265</v>
-      </c>
-      <c r="B38" s="104" t="n">
-        <v>21201</v>
-      </c>
-      <c r="C38" s="104">
-        <f t="array" ref="C38">C37+B38</f>
-        <v>8523625.0</v>
-      </c>
-      <c r="D38" s="27" t="n"/>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="27" t="n"/>
-      <c r="H38" s="27" t="n"/>
-      <c r="I38" s="27" t="n"/>
-      <c r="J38" s="27" t="n"/>
-      <c r="K38" s="27" t="n"/>
-      <c r="L38" s="27" t="n"/>
-      <c r="M38" s="27" t="n"/>
-      <c r="N38" s="27" t="n"/>
-      <c r="O38" s="27" t="n"/>
-      <c r="P38" s="27" t="n"/>
-    </row>
-    <row r="39" ht="13.65" customHeight="1" s="93">
-      <c r="A39" s="110" t="n">
-        <v>44266</v>
-      </c>
-      <c r="B39" s="104" t="n">
-        <v>3231</v>
-      </c>
-      <c r="C39" s="104">
-        <f t="array" ref="C39">C38+B39</f>
-        <v>8526856.0</v>
-      </c>
-      <c r="D39" s="27" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="27" t="n"/>
-      <c r="G39" s="27" t="n"/>
-      <c r="H39" s="27" t="n"/>
-      <c r="I39" s="27" t="n"/>
-      <c r="J39" s="27" t="n"/>
-      <c r="K39" s="27" t="n"/>
-      <c r="L39" s="27" t="n"/>
-      <c r="M39" s="27" t="n"/>
-      <c r="N39" s="27" t="n"/>
-      <c r="O39" s="27" t="n"/>
-      <c r="P39" s="27" t="n"/>
-    </row>
-    <row r="40" ht="13.65" customHeight="1" s="93">
-      <c r="A40" s="110" t="n">
-        <v>44267</v>
-      </c>
-      <c r="B40" s="104" t="n">
-        <v>127599</v>
-      </c>
-      <c r="C40" s="104">
-        <f t="array" ref="C40">C39+B40</f>
-        <v>8654455.0</v>
-      </c>
-      <c r="D40" s="27" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="27" t="n"/>
-      <c r="H40" s="27" t="n"/>
-      <c r="I40" s="27" t="n"/>
-      <c r="J40" s="27" t="n"/>
-      <c r="K40" s="27" t="n"/>
-      <c r="L40" s="27" t="n"/>
-      <c r="M40" s="27" t="n"/>
-      <c r="N40" s="27" t="n"/>
-      <c r="O40" s="27" t="n"/>
-      <c r="P40" s="27" t="n"/>
-    </row>
+    <row r="1" ht="13.65" customHeight="1" s="102">
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>AUD</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>CAD</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>CHF</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>CNH</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>NZD</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>AUDJPY</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>AUDUSD</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>EURCNH</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>EURJPY</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>EURUSD</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>GBPCNH</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>GBPNZD</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>GBPUSD</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>NZDUSD</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>USDCNY</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>USDHKD</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="13.65" customHeight="1" s="102">
+      <c r="A2" s="117" t="n">
+        <v>45324</v>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>6</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="3" ht="13.65" customHeight="1" s="102">
+      <c r="A3" s="117" t="n">
+        <v>45324.41666666666</v>
+      </c>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6</v>
+      </c>
+      <c r="S3" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="4" ht="13.65" customHeight="1" s="102"/>
+    <row r="5" ht="13.65" customHeight="1" s="102"/>
+    <row r="6" ht="13.65" customHeight="1" s="102"/>
+    <row r="7" ht="13.65" customHeight="1" s="102"/>
+    <row r="8" ht="13.65" customHeight="1" s="102"/>
+    <row r="9" ht="13.65" customHeight="1" s="102"/>
+    <row r="10" ht="13.65" customHeight="1" s="102"/>
+    <row r="11" ht="13.65" customHeight="1" s="102"/>
+    <row r="12" ht="13.65" customHeight="1" s="102"/>
+    <row r="13" ht="13.65" customHeight="1" s="102"/>
+    <row r="14" ht="13.65" customHeight="1" s="102"/>
+    <row r="15" ht="13.65" customHeight="1" s="102"/>
+    <row r="16" ht="13.65" customHeight="1" s="102"/>
+    <row r="17" ht="13.65" customHeight="1" s="102"/>
+    <row r="18" ht="13.65" customHeight="1" s="102"/>
+    <row r="19" ht="13.65" customHeight="1" s="102"/>
   </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
-  <pageSetup orientation="landscape" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05278" bottom="1.05278" header="0.7875" footer="0.7875"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
   <headerFooter>
-    <oddHeader/>
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12 &amp;K000000PARAMS</oddHeader>
     <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
     <evenHeader/>
     <evenFooter/>
@@ -7714,15 +6862,15 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="1"/>
-    <col width="9.851559999999999" customWidth="1" style="90" min="2" max="2"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="3" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="1"/>
+    <col width="9.851559999999999" customWidth="1" style="99" min="2" max="2"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="3" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="93">
-      <c r="A1" s="91" t="n"/>
-      <c r="B1" s="92" t="inlineStr">
+    <row r="1" ht="16" customHeight="1" s="102">
+      <c r="A1" s="100" t="n"/>
+      <c r="B1" s="101" t="inlineStr">
         <is>
           <t>USDCNH</t>
         </is>
@@ -7731,130 +6879,130 @@
       <c r="D1" s="27" t="n"/>
       <c r="E1" s="27" t="n"/>
     </row>
-    <row r="2" ht="16" customHeight="1" s="93">
-      <c r="A2" s="92" t="inlineStr">
+    <row r="2" ht="16" customHeight="1" s="102">
+      <c r="A2" s="101" t="inlineStr">
         <is>
           <t>1w</t>
         </is>
       </c>
-      <c r="B2" s="91" t="n">
+      <c r="B2" s="100" t="n">
         <v>2.6</v>
       </c>
       <c r="C2" s="27" t="n"/>
       <c r="D2" s="27" t="n"/>
       <c r="E2" s="27" t="n"/>
     </row>
-    <row r="3" ht="16" customHeight="1" s="93">
-      <c r="A3" s="92" t="inlineStr">
+    <row r="3" ht="16" customHeight="1" s="102">
+      <c r="A3" s="101" t="inlineStr">
         <is>
           <t>2w</t>
         </is>
       </c>
-      <c r="B3" s="91" t="n">
+      <c r="B3" s="100" t="n">
         <v>2.3</v>
       </c>
       <c r="C3" s="27" t="n"/>
       <c r="D3" s="27" t="n"/>
       <c r="E3" s="27" t="n"/>
     </row>
-    <row r="4" ht="16" customHeight="1" s="93">
-      <c r="A4" s="92" t="inlineStr">
+    <row r="4" ht="16" customHeight="1" s="102">
+      <c r="A4" s="101" t="inlineStr">
         <is>
           <t>1m</t>
         </is>
       </c>
-      <c r="B4" s="91" t="n">
+      <c r="B4" s="100" t="n">
         <v>1.85</v>
       </c>
       <c r="C4" s="27" t="n"/>
       <c r="D4" s="27" t="n"/>
       <c r="E4" s="27" t="n"/>
     </row>
-    <row r="5" ht="16" customHeight="1" s="93">
-      <c r="A5" s="92" t="inlineStr">
+    <row r="5" ht="16" customHeight="1" s="102">
+      <c r="A5" s="101" t="inlineStr">
         <is>
           <t>2m</t>
         </is>
       </c>
-      <c r="B5" s="91" t="n">
+      <c r="B5" s="100" t="n">
         <v>1.6</v>
       </c>
       <c r="C5" s="27" t="n"/>
       <c r="D5" s="27" t="n"/>
       <c r="E5" s="27" t="n"/>
     </row>
-    <row r="6" ht="16" customHeight="1" s="93">
-      <c r="A6" s="92" t="inlineStr">
+    <row r="6" ht="16" customHeight="1" s="102">
+      <c r="A6" s="101" t="inlineStr">
         <is>
           <t>3m</t>
         </is>
       </c>
-      <c r="B6" s="91" t="n">
+      <c r="B6" s="100" t="n">
         <v>1.45</v>
       </c>
       <c r="C6" s="27" t="n"/>
       <c r="D6" s="27" t="n"/>
       <c r="E6" s="27" t="n"/>
     </row>
-    <row r="7" ht="16" customHeight="1" s="93">
-      <c r="A7" s="92" t="inlineStr">
+    <row r="7" ht="16" customHeight="1" s="102">
+      <c r="A7" s="101" t="inlineStr">
         <is>
           <t>6m</t>
         </is>
       </c>
-      <c r="B7" s="91" t="n">
+      <c r="B7" s="100" t="n">
         <v>1.2</v>
       </c>
       <c r="C7" s="27" t="n"/>
       <c r="D7" s="27" t="n"/>
       <c r="E7" s="27" t="n"/>
     </row>
-    <row r="8" ht="16" customHeight="1" s="93">
-      <c r="A8" s="92" t="inlineStr">
+    <row r="8" ht="16" customHeight="1" s="102">
+      <c r="A8" s="101" t="inlineStr">
         <is>
           <t>9m</t>
         </is>
       </c>
-      <c r="B8" s="91" t="n">
+      <c r="B8" s="100" t="n">
         <v>1.1</v>
       </c>
       <c r="C8" s="27" t="n"/>
       <c r="D8" s="27" t="n"/>
       <c r="E8" s="27" t="n"/>
     </row>
-    <row r="9" ht="16" customHeight="1" s="93">
-      <c r="A9" s="92" t="inlineStr">
+    <row r="9" ht="16" customHeight="1" s="102">
+      <c r="A9" s="101" t="inlineStr">
         <is>
           <t>1y</t>
         </is>
       </c>
-      <c r="B9" s="91" t="n">
+      <c r="B9" s="100" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="27" t="n"/>
       <c r="D9" s="27" t="n"/>
       <c r="E9" s="27" t="n"/>
     </row>
-    <row r="10" ht="16" customHeight="1" s="93">
-      <c r="A10" s="92" t="inlineStr">
+    <row r="10" ht="16" customHeight="1" s="102">
+      <c r="A10" s="101" t="inlineStr">
         <is>
           <t>2y</t>
         </is>
       </c>
-      <c r="B10" s="91" t="n">
+      <c r="B10" s="100" t="n">
         <v>0.9</v>
       </c>
       <c r="C10" s="27" t="n"/>
       <c r="D10" s="27" t="n"/>
       <c r="E10" s="27" t="n"/>
     </row>
-    <row r="11" ht="16" customHeight="1" s="93">
-      <c r="A11" s="92" t="inlineStr">
+    <row r="11" ht="16" customHeight="1" s="102">
+      <c r="A11" s="101" t="inlineStr">
         <is>
           <t>3y</t>
         </is>
       </c>
-      <c r="B11" s="91" t="n">
+      <c r="B11" s="100" t="n">
         <v>0.85</v>
       </c>
       <c r="C11" s="27" t="n"/>
@@ -7875,6 +7023,126 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>hazard</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>weak_share</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>weak_jump</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>weak_vol</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>strong_jump</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>strong_vol</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>blend</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>solve_hazard</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>USDHKD</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>warn</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>85</v>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>100</v>
+      </c>
+      <c r="L2" t="n">
+        <v>25</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7884,11 +7152,11 @@
   <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>PAIRS</t>
@@ -7903,7 +7171,7 @@
       <c r="D1" s="27" t="n"/>
       <c r="E1" s="27" t="n"/>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="29" t="inlineStr">
         <is>
           <t>USDJPY</t>
@@ -7918,7 +7186,7 @@
       <c r="D2" s="27" t="n"/>
       <c r="E2" s="27" t="n"/>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="29" t="inlineStr">
         <is>
           <t>USDCNH</t>
@@ -7933,7 +7201,7 @@
       <c r="D3" s="27" t="n"/>
       <c r="E3" s="27" t="n"/>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="29" t="inlineStr">
         <is>
           <t>USDCNY</t>
@@ -7948,7 +7216,7 @@
       <c r="D4" s="27" t="n"/>
       <c r="E4" s="27" t="n"/>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="29" t="inlineStr">
         <is>
           <t>EURUSD</t>
@@ -7963,7 +7231,7 @@
       <c r="D5" s="27" t="n"/>
       <c r="E5" s="27" t="n"/>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="29" t="inlineStr">
         <is>
           <t>GBPUSD</t>
@@ -7978,7 +7246,7 @@
       <c r="D6" s="27" t="n"/>
       <c r="E6" s="27" t="n"/>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="29" t="inlineStr">
         <is>
           <t>AUDUSD</t>
@@ -7993,7 +7261,7 @@
       <c r="D7" s="27" t="n"/>
       <c r="E7" s="27" t="n"/>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="29" t="inlineStr">
         <is>
           <t>NZDUSD</t>
@@ -8008,7 +7276,7 @@
       <c r="D8" s="27" t="n"/>
       <c r="E8" s="27" t="n"/>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="29" t="inlineStr">
         <is>
           <t>EURJPY</t>
@@ -8023,7 +7291,7 @@
       <c r="D9" s="27" t="n"/>
       <c r="E9" s="27" t="n"/>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="29" t="inlineStr">
         <is>
           <t>AUDJPY</t>
@@ -8038,7 +7306,7 @@
       <c r="D10" s="27" t="n"/>
       <c r="E10" s="27" t="n"/>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="29" t="inlineStr">
         <is>
           <t>EURGBP</t>
@@ -8049,7 +7317,7 @@
       <c r="D11" s="27" t="n"/>
       <c r="E11" s="27" t="n"/>
     </row>
-    <row r="12" ht="13.65" customHeight="1" s="93">
+    <row r="12" ht="13.65" customHeight="1" s="102">
       <c r="A12" s="29" t="inlineStr">
         <is>
           <t>GBPNZD</t>
@@ -8060,7 +7328,7 @@
       <c r="D12" s="27" t="n"/>
       <c r="E12" s="27" t="n"/>
     </row>
-    <row r="13" ht="13.65" customHeight="1" s="93">
+    <row r="13" ht="13.65" customHeight="1" s="102">
       <c r="A13" s="29" t="inlineStr">
         <is>
           <t>EURCNH</t>
@@ -8071,7 +7339,7 @@
       <c r="D13" s="27" t="n"/>
       <c r="E13" s="27" t="n"/>
     </row>
-    <row r="14" ht="13.65" customHeight="1" s="93">
+    <row r="14" ht="13.65" customHeight="1" s="102">
       <c r="A14" s="29" t="inlineStr">
         <is>
           <t>GBPCNH</t>
@@ -8082,7 +7350,7 @@
       <c r="D14" s="27" t="n"/>
       <c r="E14" s="27" t="n"/>
     </row>
-    <row r="15" ht="13.65" customHeight="1" s="93">
+    <row r="15" ht="13.65" customHeight="1" s="102">
       <c r="A15" s="29" t="inlineStr">
         <is>
           <t>USDHKD</t>
@@ -8116,11 +7384,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -8147,7 +7415,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
@@ -8168,7 +7436,7 @@
         <v>-1.719</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
@@ -8189,7 +7457,7 @@
         <v>-1.9485</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
@@ -8210,7 +7478,7 @@
         <v>-2.356</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
@@ -8231,7 +7499,7 @@
         <v>-2.299</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
@@ -8252,7 +7520,7 @@
         <v>-2.546</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
@@ -8273,7 +7541,7 @@
         <v>-2.7645</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
@@ -8294,7 +7562,7 @@
         <v>-3.021</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
@@ -8315,7 +7583,7 @@
         <v>-3.135</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -8336,7 +7604,7 @@
         <v>-3.249</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -8380,11 +7648,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -8411,7 +7679,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
@@ -8432,7 +7700,7 @@
         <v>-0.82325</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
@@ -8453,7 +7721,7 @@
         <v>-0.925</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
@@ -8474,7 +7742,7 @@
         <v>-1.10075</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
@@ -8495,7 +7763,7 @@
         <v>-1.077625</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
@@ -8516,7 +7784,7 @@
         <v>-1.373625</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
@@ -8537,7 +7805,7 @@
         <v>-1.493875</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
@@ -8558,7 +7826,7 @@
         <v>-1.7625</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
@@ -8579,7 +7847,7 @@
         <v>-2.025</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -8600,7 +7868,7 @@
         <v>-2.1</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -8644,11 +7912,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -8675,7 +7943,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
@@ -8696,7 +7964,7 @@
         <v>0.624</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
@@ -8717,7 +7985,7 @@
         <v>0.909</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
@@ -8738,7 +8006,7 @@
         <v>0.936</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
@@ -8759,7 +8027,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
@@ -8780,7 +8048,7 @@
         <v>1.0125</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
@@ -8801,7 +8069,7 @@
         <v>1.0395</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
@@ -8822,7 +8090,7 @@
         <v>1.0035</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
@@ -8843,7 +8111,7 @@
         <v>1.0575</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -8864,7 +8132,7 @@
         <v>1.044</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
@@ -8906,247 +8174,260 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="15" customHeight="1" outlineLevelRow="0"/>
+  <cols>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="94" t="inlineStr">
+    <row r="1" ht="13.65" customHeight="1" s="102">
+      <c r="A1" s="42" t="inlineStr">
         <is>
           <t>expiry</t>
         </is>
       </c>
-      <c r="B1" s="94" t="inlineStr">
+      <c r="B1" s="43" t="inlineStr">
         <is>
           <t>ST 10D</t>
         </is>
       </c>
-      <c r="C1" s="94" t="inlineStr">
+      <c r="C1" s="42" t="inlineStr">
         <is>
           <t>ST 25D</t>
         </is>
       </c>
-      <c r="D1" s="94" t="inlineStr">
+      <c r="D1" s="42" t="inlineStr">
         <is>
           <t>RR 25D</t>
         </is>
       </c>
-      <c r="E1" s="94" t="inlineStr">
+      <c r="E1" s="43" t="inlineStr">
         <is>
           <t>RR 10D</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="94" t="inlineStr">
+    <row r="2" ht="13.65" customHeight="1" s="102">
+      <c r="A2" s="44" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="95">
-        <f>C2*3.1</f>
+      <c r="B2" s="45">
+        <f t="array" ref="B2">C2*3.1</f>
         <v>0.33325</v>
       </c>
-      <c r="C2" s="94" t="n">
+      <c r="C2" s="46" t="n">
         <v>0.1075</v>
       </c>
-      <c r="D2" s="94" t="n">
+      <c r="D2" s="47" t="n">
         <v>0.34</v>
       </c>
-      <c r="E2" s="95">
-        <f>D2*1.8</f>
+      <c r="E2" s="48">
+        <f t="array" ref="E2">D2*1.8</f>
         <v>0.612</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="94" t="inlineStr">
+    <row r="3" ht="13.65" customHeight="1" s="102">
+      <c r="A3" s="44" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="95">
-        <f>C3*3.1</f>
+      <c r="B3" s="45">
+        <f t="array" ref="B3">C3*3.1</f>
         <v>0.3875</v>
       </c>
-      <c r="C3" s="94" t="n">
+      <c r="C3" s="46" t="n">
         <v>0.125</v>
       </c>
-      <c r="D3" s="94" t="n">
+      <c r="D3" s="47" t="n">
         <v>0.39</v>
       </c>
-      <c r="E3" s="95">
-        <f>D3*1.8</f>
+      <c r="E3" s="48">
+        <f t="array" ref="E3">D3*1.8</f>
         <v>0.702</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="94" t="inlineStr">
+    <row r="4" ht="13.65" customHeight="1" s="102">
+      <c r="A4" s="44" t="inlineStr">
         <is>
           <t>3W</t>
         </is>
       </c>
-      <c r="B4" s="95">
-        <f>C4*3.1</f>
+      <c r="B4" s="45">
+        <f t="array" ref="B4">C4*3.1</f>
         <v>0.465</v>
       </c>
-      <c r="C4" s="94" t="n">
+      <c r="C4" s="46" t="n">
         <v>0.15</v>
       </c>
-      <c r="D4" s="94" t="n">
+      <c r="D4" s="47" t="n">
         <v>0.425</v>
       </c>
-      <c r="E4" s="95">
-        <f>D4*1.8</f>
+      <c r="E4" s="48">
+        <f t="array" ref="E4">D4*1.8</f>
         <v>0.765</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="94" t="inlineStr">
+    <row r="5" ht="13.65" customHeight="1" s="102">
+      <c r="A5" s="44" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B5" s="95">
-        <f>C5*3.1</f>
+      <c r="B5" s="45">
+        <f t="array" ref="B5">C5*3.1</f>
         <v>0.403</v>
       </c>
-      <c r="C5" s="94" t="n">
+      <c r="C5" s="46" t="n">
         <v>0.13</v>
       </c>
-      <c r="D5" s="94" t="n">
+      <c r="D5" s="47" t="n">
         <v>0.49</v>
       </c>
-      <c r="E5" s="95">
-        <f>D5*1.85</f>
+      <c r="E5" s="48">
+        <f t="array" ref="E5">D5*1.85</f>
         <v>0.9065</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="94" t="inlineStr">
+    <row r="6" ht="13.65" customHeight="1" s="102">
+      <c r="A6" s="44" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B6" s="95">
-        <f>C6*3.1</f>
+      <c r="B6" s="45">
+        <f t="array" ref="B6">C6*3.1</f>
         <v>0.4805</v>
       </c>
-      <c r="C6" s="94" t="n">
+      <c r="C6" s="46" t="n">
         <v>0.155</v>
       </c>
-      <c r="D6" s="94" t="n">
+      <c r="D6" s="47" t="n">
         <v>0.575</v>
       </c>
-      <c r="E6" s="95">
-        <f>D6*1.85</f>
+      <c r="E6" s="48">
+        <f t="array" ref="E6">D6*1.85</f>
         <v>1.06375</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="94" t="inlineStr">
+    <row r="7" ht="13.65" customHeight="1" s="102">
+      <c r="A7" s="44" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B7" s="95">
-        <f>C7*3.1</f>
+      <c r="B7" s="45">
+        <f t="array" ref="B7">C7*3.1</f>
         <v>0.558</v>
       </c>
-      <c r="C7" s="94" t="n">
+      <c r="C7" s="46" t="n">
         <v>0.18</v>
       </c>
-      <c r="D7" s="94" t="n">
+      <c r="D7" s="47" t="n">
         <v>0.6475</v>
       </c>
-      <c r="E7" s="95">
-        <f>D7*1.85</f>
+      <c r="E7" s="48">
+        <f t="array" ref="E7">D7*1.85</f>
         <v>1.197875</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="94" t="inlineStr">
+    <row r="8" ht="13.65" customHeight="1" s="102">
+      <c r="A8" s="44" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B8" s="95">
-        <f>C8*3.1</f>
+      <c r="B8" s="45">
+        <f t="array" ref="B8">C8*3.1</f>
         <v>0.72075</v>
       </c>
-      <c r="C8" s="94" t="n">
+      <c r="C8" s="46" t="n">
         <v>0.2325</v>
       </c>
-      <c r="D8" s="94" t="n">
+      <c r="D8" s="47" t="n">
         <v>0.7875</v>
       </c>
-      <c r="E8" s="95">
-        <f>D8*1.85</f>
+      <c r="E8" s="48">
+        <f t="array" ref="E8">D8*1.85</f>
         <v>1.456875</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="94" t="inlineStr">
+    <row r="9" ht="13.65" customHeight="1" s="102">
+      <c r="A9" s="44" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B9" s="95">
-        <f>C9*3.1</f>
+      <c r="B9" s="45">
+        <f t="array" ref="B9">C9*3.1</f>
         <v>0.79825</v>
       </c>
-      <c r="C9" s="94" t="n">
+      <c r="C9" s="46" t="n">
         <v>0.2575</v>
       </c>
-      <c r="D9" s="94" t="n">
+      <c r="D9" s="47" t="n">
         <v>0.8625</v>
       </c>
-      <c r="E9" s="95">
-        <f>D9*1.85</f>
+      <c r="E9" s="48">
+        <f t="array" ref="E9">D9*1.85</f>
         <v>1.595625</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="94" t="inlineStr">
+    <row r="10" ht="13.65" customHeight="1" s="102">
+      <c r="A10" s="44" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B10" s="95">
-        <f>C10*3.2</f>
+      <c r="B10" s="45">
+        <f t="array" ref="B10">C10*3.2</f>
         <v>0.84</v>
       </c>
-      <c r="C10" s="94" t="n">
+      <c r="C10" s="46" t="n">
         <v>0.2625</v>
       </c>
-      <c r="D10" s="94" t="n">
+      <c r="D10" s="47" t="n">
         <v>0.9125</v>
       </c>
-      <c r="E10" s="95">
-        <f>D10*1.85</f>
+      <c r="E10" s="48">
+        <f t="array" ref="E10">D10*1.85</f>
         <v>1.688125</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="94" t="inlineStr">
+    <row r="11" ht="13.65" customHeight="1" s="102">
+      <c r="A11" s="44" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B11" s="95">
-        <f>C11*3.2</f>
+      <c r="B11" s="49">
+        <f t="array" ref="B11">C11*3.2</f>
         <v>1.08</v>
       </c>
-      <c r="C11" s="94" t="n">
+      <c r="C11" s="46" t="n">
         <v>0.3375</v>
       </c>
-      <c r="D11" s="94" t="n">
+      <c r="D11" s="47" t="n">
         <v>0.8675</v>
       </c>
-      <c r="E11" s="95">
-        <f>D11*1.85</f>
+      <c r="E11" s="50">
+        <f t="array" ref="E11">D11*1.85</f>
         <v>1.604875</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -9159,11 +8440,11 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -9190,191 +8471,191 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
         </is>
       </c>
-      <c r="B2" s="96">
+      <c r="B2" s="103">
         <f t="array" ref="B2">C2*3.4</f>
         <v>0.6205</v>
       </c>
-      <c r="C2" s="97" t="n">
+      <c r="C2" s="104" t="n">
         <v>0.1825</v>
       </c>
-      <c r="D2" s="98" t="n">
+      <c r="D2" s="105" t="n">
         <v>0.385</v>
       </c>
-      <c r="E2" s="99">
+      <c r="E2" s="106">
         <f t="array" ref="E2">D2*2.05</f>
         <v>0.78925</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
         </is>
       </c>
-      <c r="B3" s="96">
+      <c r="B3" s="103">
         <f t="array" ref="B3">C3*3.4</f>
         <v>0.6375</v>
       </c>
-      <c r="C3" s="97" t="n">
+      <c r="C3" s="104" t="n">
         <v>0.1875</v>
       </c>
-      <c r="D3" s="98" t="n">
+      <c r="D3" s="105" t="n">
         <v>0.45</v>
       </c>
-      <c r="E3" s="99">
+      <c r="E3" s="106">
         <f t="array" ref="E3">D3*2.15</f>
         <v>0.9675</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>1M</t>
         </is>
       </c>
-      <c r="B4" s="96">
+      <c r="B4" s="103">
         <f t="array" ref="B4">C4*3.4</f>
         <v>0.731</v>
       </c>
-      <c r="C4" s="97" t="n">
+      <c r="C4" s="104" t="n">
         <v>0.215</v>
       </c>
-      <c r="D4" s="98" t="n">
+      <c r="D4" s="105" t="n">
         <v>0.525</v>
       </c>
-      <c r="E4" s="99">
+      <c r="E4" s="106">
         <f t="array" ref="E4">D4*2.3</f>
         <v>1.2075</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>2M</t>
         </is>
       </c>
-      <c r="B5" s="96">
+      <c r="B5" s="103">
         <f t="array" ref="B5">C5*3.4</f>
         <v>0.816</v>
       </c>
-      <c r="C5" s="97" t="n">
+      <c r="C5" s="104" t="n">
         <v>0.24</v>
       </c>
-      <c r="D5" s="98" t="n">
+      <c r="D5" s="105" t="n">
         <v>0.66</v>
       </c>
-      <c r="E5" s="99">
+      <c r="E5" s="106">
         <f t="array" ref="E5">D5*2.3</f>
         <v>1.518</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>3M</t>
         </is>
       </c>
-      <c r="B6" s="96">
+      <c r="B6" s="103">
         <f t="array" ref="B6">C6*3.4</f>
         <v>0.867</v>
       </c>
-      <c r="C6" s="97" t="n">
+      <c r="C6" s="104" t="n">
         <v>0.255</v>
       </c>
-      <c r="D6" s="98" t="n">
+      <c r="D6" s="105" t="n">
         <v>0.74</v>
       </c>
-      <c r="E6" s="99">
+      <c r="E6" s="106">
         <f t="array" ref="E6">D6*2.3</f>
         <v>1.702</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>6M</t>
         </is>
       </c>
-      <c r="B7" s="96">
+      <c r="B7" s="103">
         <f t="array" ref="B7">C7*3.4</f>
         <v>0.986</v>
       </c>
-      <c r="C7" s="97" t="n">
+      <c r="C7" s="104" t="n">
         <v>0.29</v>
       </c>
-      <c r="D7" s="98" t="n">
+      <c r="D7" s="105" t="n">
         <v>0.95</v>
       </c>
-      <c r="E7" s="99">
+      <c r="E7" s="106">
         <f t="array" ref="E7">D7*2.3</f>
         <v>2.185</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>9M</t>
         </is>
       </c>
-      <c r="B8" s="96">
+      <c r="B8" s="103">
         <f t="array" ref="B8">C8*3.4</f>
         <v>1.122</v>
       </c>
-      <c r="C8" s="97" t="n">
+      <c r="C8" s="104" t="n">
         <v>0.33</v>
       </c>
-      <c r="D8" s="98" t="n">
+      <c r="D8" s="105" t="n">
         <v>1.07</v>
       </c>
-      <c r="E8" s="99">
+      <c r="E8" s="106">
         <f t="array" ref="E8">D8*2.3</f>
         <v>2.461</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="B9" s="96">
+      <c r="B9" s="103">
         <f t="array" ref="B9">C9*3.4</f>
         <v>1.207</v>
       </c>
-      <c r="C9" s="97" t="n">
+      <c r="C9" s="104" t="n">
         <v>0.355</v>
       </c>
-      <c r="D9" s="98" t="n">
+      <c r="D9" s="105" t="n">
         <v>1.15</v>
       </c>
-      <c r="E9" s="99">
+      <c r="E9" s="106">
         <f t="array" ref="E9">D9*2.3</f>
         <v>2.645</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>2Y</t>
         </is>
       </c>
-      <c r="B10" s="100">
+      <c r="B10" s="107">
         <f t="array" ref="B10">C10*3.4</f>
         <v>1.292</v>
       </c>
-      <c r="C10" s="97" t="n">
+      <c r="C10" s="104" t="n">
         <v>0.38</v>
       </c>
-      <c r="D10" s="98" t="n">
+      <c r="D10" s="105" t="n">
         <v>1.25</v>
       </c>
-      <c r="E10" s="101">
+      <c r="E10" s="108">
         <f t="array" ref="E10">D10*2.3</f>
         <v>2.875</v>
       </c>
@@ -9402,11 +8683,11 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
   <cols>
-    <col width="8.851559999999999" customWidth="1" style="90" min="1" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="90" min="6" max="16384"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="5"/>
+    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1" s="93">
+    <row r="1" ht="13.65" customHeight="1" s="102">
       <c r="A1" s="29" t="inlineStr">
         <is>
           <t>expiry</t>
@@ -9433,7 +8714,7 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="13.65" customHeight="1" s="93">
+    <row r="2" ht="13.65" customHeight="1" s="102">
       <c r="A2" s="32" t="inlineStr">
         <is>
           <t>1W</t>
@@ -9454,7 +8735,7 @@
         <v>0.1235</v>
       </c>
     </row>
-    <row r="3" ht="13.65" customHeight="1" s="93">
+    <row r="3" ht="13.65" customHeight="1" s="102">
       <c r="A3" s="32" t="inlineStr">
         <is>
           <t>2W</t>
@@ -9475,7 +8756,7 @@
         <v>0.252</v>
       </c>
     </row>
-    <row r="4" ht="13.65" customHeight="1" s="93">
+    <row r="4" ht="13.65" customHeight="1" s="102">
       <c r="A4" s="32" t="inlineStr">
         <is>
           <t>3W</t>
@@ -9496,7 +8777,7 @@
         <v>0.261</v>
       </c>
     </row>
-    <row r="5" ht="13.65" customHeight="1" s="93">
+    <row r="5" ht="13.65" customHeight="1" s="102">
       <c r="A5" s="32" t="inlineStr">
         <is>
           <t>1M</t>
@@ -9517,7 +8798,7 @@
         <v>0.2835</v>
       </c>
     </row>
-    <row r="6" ht="13.65" customHeight="1" s="93">
+    <row r="6" ht="13.65" customHeight="1" s="102">
       <c r="A6" s="32" t="inlineStr">
         <is>
           <t>2M</t>
@@ -9538,7 +8819,7 @@
         <v>0.333</v>
       </c>
     </row>
-    <row r="7" ht="13.65" customHeight="1" s="93">
+    <row r="7" ht="13.65" customHeight="1" s="102">
       <c r="A7" s="32" t="inlineStr">
         <is>
           <t>3M</t>
@@ -9559,7 +8840,7 @@
         <v>0.414</v>
       </c>
     </row>
-    <row r="8" ht="13.65" customHeight="1" s="93">
+    <row r="8" ht="13.65" customHeight="1" s="102">
       <c r="A8" s="32" t="inlineStr">
         <is>
           <t>6M</t>
@@ -9580,7 +8861,7 @@
         <v>0.639</v>
       </c>
     </row>
-    <row r="9" ht="13.65" customHeight="1" s="93">
+    <row r="9" ht="13.65" customHeight="1" s="102">
       <c r="A9" s="32" t="inlineStr">
         <is>
           <t>9M</t>
@@ -9601,7 +8882,7 @@
         <v>0.675</v>
       </c>
     </row>
-    <row r="10" ht="13.65" customHeight="1" s="93">
+    <row r="10" ht="13.65" customHeight="1" s="102">
       <c r="A10" s="32" t="inlineStr">
         <is>
           <t>1Y</t>
@@ -9622,7 +8903,7 @@
         <v>0.828</v>
       </c>
     </row>
-    <row r="11" ht="13.65" customHeight="1" s="93">
+    <row r="11" ht="13.65" customHeight="1" s="102">
       <c r="A11" s="32" t="inlineStr">
         <is>
           <t>2Y</t>

--- a/files/vol_marks.xlsx
+++ b/files/vol_marks.xlsx
@@ -30,6 +30,9 @@
     <sheet name="EVENTS" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Vega Weights" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="BANDS" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="PEG_BANDS" sheetId="25" r:id="rIdCfg25"/>
+    <sheet name="KACE_SPREADS" sheetId="26" r:id="rIdCfg26"/>
+    <sheet name="HOLIDAYS" sheetId="27" r:id="rIdCfg27"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -7143,6 +7146,650 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="78" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Managed / pegged trading bands: pair, lower, upper, note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># These are policy settings, not market data. Check them against the central</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># bank before use, and delete a pair whose regime changes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># A band here means a HARD, defended range for the spot. Only list a pair on</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># this tab if that is true: the model gives strikes outside the band zero</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># in-band value, which is right for a defended peg and wrong for anything else.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Not to be confused with the BANDS tab, which is the marking *treatment* for a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># pegged pair -- hazard, jump sizes, blend. The defended range itself is here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pair</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">lower</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">upper</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">note</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDHKD</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>7.75</v>
+      </c>
+      <c r="C13">
+        <v>7.85</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HKMA Convertibility Undertakings under the Linked Exchange Rate System</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Deliberately NOT listed:</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#   USDCNY - the +/-2% limit is around a daily fixing, so the band moves every</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#            day and is not a fixed range for a multi-month option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#   USDCNH - offshore, not subject to the onshore limit at all.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#   DKK    - ERM II central rate 7.46038 with a +/-2.25% formal band, but the</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#            Nationalbank runs a far tighter de facto range; add it only with</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#            a range you are prepared to defend.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># The kACE feed: which tenors are posted as pillars, and the ATM bid/offer</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># width at each, in volatility points.  Read by volkit/kace.py.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># The tenors listed for a pair are exactly the pillars posted for it, so a</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># pair with no rows here cannot be posted, and a tenor listed here with no</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># wing marks in the workbook is refused by name.  O/N is the one-day option</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># and borrows the shortest quoted tenor's wings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># A day between two pillars takes the spread of the earlier one; a day before</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># the O/N expiry takes O/N's.  These rows are the USDCNH sheet's column L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pair</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tenor</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">spread</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O/N</t>
+        </is>
+      </c>
+      <c r="C12">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1W</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2W</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1M</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2M</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3M</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6M</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9M</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">USDCNH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1Y</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>0.2</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Holiday dates no rule derives: country, date, remove.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Lunar-calendar holidays are published annually and cannot be worked out from</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># rules, so they are listed here. A row with remove = yes takes a date away</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># that the built-in rules would otherwise make a holiday.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Dates are YYYY-MM-DD. A '#' in the first column makes the whole row a note.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">country</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">date</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">remove</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Chinese New Year 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-29</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-01-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-02-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2025-02-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t xml:space="preserve"># Chinese New Year 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-19</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-02-20</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/files/vol_marks.xlsx
+++ b/files/vol_marks.xlsx
@@ -30,9 +30,9 @@
     <sheet name="EVENTS" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Vega Weights" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="BANDS" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="PEG_BANDS" sheetId="25" r:id="rIdCfg25"/>
-    <sheet name="KACE_SPREADS" sheetId="26" r:id="rIdCfg26"/>
-    <sheet name="HOLIDAYS" sheetId="27" r:id="rIdCfg27"/>
+    <sheet name="PEG_BANDS" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="KACE_SPREADS" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="HOLIDAYS" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -40,7 +40,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="&quot; &quot;* #,##0.000&quot; &quot;;&quot; &quot;* (#,##0.000);&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
     <numFmt numFmtId="166" formatCode="0.0000"/>
@@ -49,8 +49,7 @@
     <numFmt numFmtId="169" formatCode="&quot; &quot;* #,##0.00000&quot; &quot;;&quot; &quot;* (#,##0.00000);&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
     <numFmt numFmtId="170" formatCode="0.000%"/>
     <numFmt numFmtId="171" formatCode="&quot; &quot;* #,##0.00&quot; &quot;;&quot; &quot;* (#,##0.00);&quot; &quot;* &quot;-&quot;??&quot; &quot;"/>
-    <numFmt numFmtId="172" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="173" formatCode="yyyy-mm-dd hh:mm"/>
+    <numFmt numFmtId="172" formatCode="yyyy-mm-dd hh:mm"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -359,7 +358,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -709,7 +708,8 @@
     <xf numFmtId="167" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6621,208 +6621,208 @@
   </cols>
   <sheetData>
     <row r="1" ht="13.65" customHeight="1" s="102">
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="99" t="inlineStr">
         <is>
           <t>AUD</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="99" t="inlineStr">
         <is>
           <t>CAD</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="99" t="inlineStr">
         <is>
           <t>CHF</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="99" t="inlineStr">
         <is>
           <t>CNH</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="99" t="inlineStr">
         <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="99" t="inlineStr">
         <is>
           <t>GBP</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="99" t="inlineStr">
         <is>
           <t>NZD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="99" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="99" t="inlineStr">
         <is>
           <t>AUDJPY</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="99" t="inlineStr">
         <is>
           <t>AUDUSD</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="99" t="inlineStr">
         <is>
           <t>EURCNH</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="99" t="inlineStr">
         <is>
           <t>EURGBP</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="99" t="inlineStr">
         <is>
           <t>EURJPY</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="99" t="inlineStr">
         <is>
           <t>EURUSD</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="99" t="inlineStr">
         <is>
           <t>GBPCNH</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="99" t="inlineStr">
         <is>
           <t>GBPNZD</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="99" t="inlineStr">
         <is>
           <t>GBPUSD</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="99" t="inlineStr">
         <is>
           <t>NZDUSD</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="99" t="inlineStr">
         <is>
           <t>USDCNH</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="99" t="inlineStr">
         <is>
           <t>USDCNY</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="99" t="inlineStr">
         <is>
           <t>USDHKD</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="99" t="inlineStr">
         <is>
           <t>USDJPY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="13.65" customHeight="1" s="102">
-      <c r="A2" s="117" t="n">
+      <c r="A2" s="118" t="n">
         <v>45324</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="99" t="n">
         <v>0.2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="99" t="n">
         <v>0.9000000000000001</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="99" t="n">
         <v>4</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2" s="99" t="n">
         <v>6</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="99" t="n">
         <v>6.5</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2" s="99" t="n">
         <v>5.5</v>
       </c>
-      <c r="R2" t="n">
+      <c r="R2" s="99" t="n">
         <v>6</v>
       </c>
-      <c r="S2" t="n">
+      <c r="S2" s="99" t="n">
         <v>6.5</v>
       </c>
-      <c r="T2" t="n">
+      <c r="T2" s="99" t="n">
         <v>0.5</v>
       </c>
-      <c r="W2" t="n">
+      <c r="W2" s="99" t="n">
         <v>5.5</v>
       </c>
     </row>
     <row r="3" ht="13.65" customHeight="1" s="102">
-      <c r="A3" s="117" t="n">
+      <c r="A3" s="118" t="n">
         <v>45324.41666666666</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="99" t="n">
         <v>3</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="99" t="n">
         <v>0.2</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="99" t="n">
         <v>0.9000000000000001</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="99" t="n">
         <v>4</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="99" t="n">
         <v>6.5</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3" s="99" t="n">
         <v>5.5</v>
       </c>
-      <c r="R3" t="n">
+      <c r="R3" s="99" t="n">
         <v>6</v>
       </c>
-      <c r="S3" t="n">
+      <c r="S3" s="99" t="n">
         <v>6.5</v>
       </c>
-      <c r="T3" t="n">
+      <c r="T3" s="99" t="n">
         <v>0.5</v>
       </c>
-      <c r="W3" t="n">
+      <c r="W3" s="99" t="n">
         <v>5.5</v>
       </c>
     </row>
@@ -6862,167 +6862,154 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.83333" defaultRowHeight="12.75" customHeight="1" outlineLevelRow="0"/>
-  <cols>
-    <col width="8.851559999999999" customWidth="1" style="99" min="1" max="1"/>
-    <col width="9.851559999999999" customWidth="1" style="99" min="2" max="2"/>
-    <col width="8.851559999999999" customWidth="1" style="99" min="3" max="5"/>
-    <col width="8.851559999999999" customWidth="1" style="99" min="6" max="16384"/>
-  </cols>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" ht="16" customHeight="1" s="102">
-      <c r="A1" s="100" t="n"/>
-      <c r="B1" s="101" t="inlineStr">
+    <row r="1">
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t># How far each tenor moves when the anchor tenor moves one vol point.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="99" t="inlineStr">
+        <is>
+          <t># 'default' is what every pair falls back to, cell by cell; a column headed by a pair is that pair's own shape. Only ratios matter -- the anchor's own weight cancels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t># Marking screen &gt; ATM term structure &gt; bump; 'volkit vega &lt;pair&gt; --move 1'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="99" t="inlineStr">
+        <is>
+          <t>tenor</t>
+        </is>
+      </c>
+      <c r="B4" s="99" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C4" s="99" t="inlineStr">
         <is>
           <t>USDCNH</t>
         </is>
       </c>
-      <c r="C1" s="27" t="n"/>
-      <c r="D1" s="27" t="n"/>
-      <c r="E1" s="27" t="n"/>
-    </row>
-    <row r="2" ht="16" customHeight="1" s="102">
-      <c r="A2" s="101" t="inlineStr">
-        <is>
-          <t>1w</t>
-        </is>
-      </c>
-      <c r="B2" s="100" t="n">
+      <c r="D4" s="99" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="99" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="C5" s="99" t="n">
         <v>2.6</v>
       </c>
-      <c r="C2" s="27" t="n"/>
-      <c r="D2" s="27" t="n"/>
-      <c r="E2" s="27" t="n"/>
-    </row>
-    <row r="3" ht="16" customHeight="1" s="102">
-      <c r="A3" s="101" t="inlineStr">
-        <is>
-          <t>2w</t>
-        </is>
-      </c>
-      <c r="B3" s="100" t="n">
+    </row>
+    <row r="6">
+      <c r="A6" s="99" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="C6" s="99" t="n">
         <v>2.3</v>
       </c>
-      <c r="C3" s="27" t="n"/>
-      <c r="D3" s="27" t="n"/>
-      <c r="E3" s="27" t="n"/>
-    </row>
-    <row r="4" ht="16" customHeight="1" s="102">
-      <c r="A4" s="101" t="inlineStr">
-        <is>
-          <t>1m</t>
-        </is>
-      </c>
-      <c r="B4" s="100" t="n">
+    </row>
+    <row r="7">
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="C7" s="99" t="n">
         <v>1.85</v>
       </c>
-      <c r="C4" s="27" t="n"/>
-      <c r="D4" s="27" t="n"/>
-      <c r="E4" s="27" t="n"/>
-    </row>
-    <row r="5" ht="16" customHeight="1" s="102">
-      <c r="A5" s="101" t="inlineStr">
-        <is>
-          <t>2m</t>
-        </is>
-      </c>
-      <c r="B5" s="100" t="n">
+    </row>
+    <row r="8">
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="C8" s="99" t="n">
         <v>1.6</v>
       </c>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-    </row>
-    <row r="6" ht="16" customHeight="1" s="102">
-      <c r="A6" s="101" t="inlineStr">
-        <is>
-          <t>3m</t>
-        </is>
-      </c>
-      <c r="B6" s="100" t="n">
+    </row>
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="C9" s="99" t="n">
         <v>1.45</v>
       </c>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-    </row>
-    <row r="7" ht="16" customHeight="1" s="102">
-      <c r="A7" s="101" t="inlineStr">
-        <is>
-          <t>6m</t>
-        </is>
-      </c>
-      <c r="B7" s="100" t="n">
+    </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="n">
         <v>1.2</v>
       </c>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-    </row>
-    <row r="8" ht="16" customHeight="1" s="102">
-      <c r="A8" s="101" t="inlineStr">
-        <is>
-          <t>9m</t>
-        </is>
-      </c>
-      <c r="B8" s="100" t="n">
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="n">
         <v>1.1</v>
       </c>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-    </row>
-    <row r="9" ht="16" customHeight="1" s="102">
-      <c r="A9" s="101" t="inlineStr">
-        <is>
-          <t>1y</t>
-        </is>
-      </c>
-      <c r="B9" s="100" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-    </row>
-    <row r="10" ht="16" customHeight="1" s="102">
-      <c r="A10" s="101" t="inlineStr">
-        <is>
-          <t>2y</t>
-        </is>
-      </c>
-      <c r="B10" s="100" t="n">
+    </row>
+    <row r="13">
+      <c r="A13" s="99" t="inlineStr">
+        <is>
+          <t>2Y</t>
+        </is>
+      </c>
+      <c r="C13" s="99" t="n">
         <v>0.9</v>
       </c>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-    </row>
-    <row r="11" ht="16" customHeight="1" s="102">
-      <c r="A11" s="101" t="inlineStr">
-        <is>
-          <t>3y</t>
-        </is>
-      </c>
-      <c r="B11" s="100" t="n">
+    </row>
+    <row r="14">
+      <c r="A14" s="99" t="inlineStr">
+        <is>
+          <t>3Y</t>
+        </is>
+      </c>
+      <c r="C14" s="99" t="n">
         <v>0.85</v>
       </c>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811" footer="0.511811"/>
-  <pageSetup orientation="portrait" scale="100" fitToHeight="1" fitToWidth="1" firstPageNumber="1" useFirstPageNumber="0" pageOrder="downThenOver"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12 &amp;K000000&amp;P</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -7036,108 +7023,108 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="99" t="inlineStr">
         <is>
           <t>pair</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="99" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="99" t="inlineStr">
         <is>
           <t>hazard</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="99" t="inlineStr">
         <is>
           <t>weak_share</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="99" t="inlineStr">
         <is>
           <t>weak_jump</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="99" t="inlineStr">
         <is>
           <t>weak_vol</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="99" t="inlineStr">
         <is>
           <t>strong_jump</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="99" t="inlineStr">
         <is>
           <t>strong_vol</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="99" t="inlineStr">
         <is>
           <t>lower</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="99" t="inlineStr">
         <is>
           <t>upper</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="99" t="inlineStr">
         <is>
           <t>blend</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="99" t="inlineStr">
         <is>
           <t>delta</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="99" t="inlineStr">
         <is>
           <t>solve_hazard</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="99" t="inlineStr">
         <is>
           <t>USDHKD</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="99" t="inlineStr">
         <is>
           <t>warn</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="99" t="n">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="99" t="n">
         <v>85</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" s="99" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2" s="99" t="n">
         <v>10</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2" s="99" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2" s="99" t="n">
         <v>8</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" s="99" t="n">
         <v>100</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="99" t="n">
         <v>25</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -7148,645 +7135,666 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="78" customWidth="1"/>
+    <col width="12" customWidth="1" style="102" min="1" max="1"/>
+    <col width="10" customWidth="1" style="102" min="2" max="2"/>
+    <col width="10" customWidth="1" style="102" min="3" max="3"/>
+    <col width="78" customWidth="1" style="102" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Managed / pegged trading bands: pair, lower, upper, note.</t>
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t># Managed / pegged trading bands: pair, lower, upper, note.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A2" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># These are policy settings, not market data. Check them against the central</t>
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t># These are policy settings, not market data. Check them against the central</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># bank before use, and delete a pair whose regime changes.</t>
+      <c r="A4" s="99" t="inlineStr">
+        <is>
+          <t># bank before use, and delete a pair whose regime changes.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A5" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># A band here means a HARD, defended range for the spot. Only list a pair on</t>
+      <c r="A6" s="99" t="inlineStr">
+        <is>
+          <t># A band here means a HARD, defended range for the spot. Only list a pair on</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># this tab if that is true: the model gives strikes outside the band zero</t>
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t># this tab if that is true: the model gives strikes outside the band zero</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># in-band value, which is right for a defended peg and wrong for anything else.</t>
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t># in-band value, which is right for a defended peg and wrong for anything else.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Not to be confused with the BANDS tab, which is the marking *treatment* for a</t>
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t># Not to be confused with the BANDS tab, which is the marking *treatment* for a</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># pegged pair -- hazard, jump sizes, blend. The defended range itself is here.</t>
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t># pegged pair -- hazard, jump sizes, blend. The defended range itself is here.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pair</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">lower</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">upper</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">note</t>
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>lower</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr">
+        <is>
+          <t>upper</t>
+        </is>
+      </c>
+      <c r="D12" s="99" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDHKD</t>
-        </is>
-      </c>
-      <c r="B13">
+      <c r="A13" s="99" t="inlineStr">
+        <is>
+          <t>USDHKD</t>
+        </is>
+      </c>
+      <c r="B13" s="99" t="n">
         <v>7.75</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="99" t="n">
         <v>7.85</v>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HKMA Convertibility Undertakings under the Linked Exchange Rate System</t>
+      <c r="D13" s="99" t="inlineStr">
+        <is>
+          <t>HKMA Convertibility Undertakings under the Linked Exchange Rate System</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A14" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Deliberately NOT listed:</t>
+      <c r="A15" s="99" t="inlineStr">
+        <is>
+          <t># Deliberately NOT listed:</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#   USDCNY - the +/-2% limit is around a daily fixing, so the band moves every</t>
+      <c r="A16" s="99" t="inlineStr">
+        <is>
+          <t>#   USDCNY - the +/-2% limit is around a daily fixing, so the band moves every</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#            day and is not a fixed range for a multi-month option.</t>
+      <c r="A17" s="99" t="inlineStr">
+        <is>
+          <t>#            day and is not a fixed range for a multi-month option.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#   USDCNH - offshore, not subject to the onshore limit at all.</t>
+      <c r="A18" s="99" t="inlineStr">
+        <is>
+          <t>#   USDCNH - offshore, not subject to the onshore limit at all.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#   DKK    - ERM II central rate 7.46038 with a +/-2.25% formal band, but the</t>
+      <c r="A19" s="99" t="inlineStr">
+        <is>
+          <t>#   DKK    - ERM II central rate 7.46038 with a +/-2.25% formal band, but the</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#            Nationalbank runs a far tighter de facto range; add it only with</t>
+      <c r="A20" s="99" t="inlineStr">
+        <is>
+          <t>#            Nationalbank runs a far tighter de facto range; add it only with</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#            a range you are prepared to defend.</t>
+      <c r="A21" s="99" t="inlineStr">
+        <is>
+          <t>#            a range you are prepared to defend.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col width="12" customWidth="1" style="102" min="1" max="1"/>
+    <col width="10" customWidth="1" style="102" min="2" max="2"/>
+    <col width="10" customWidth="1" style="102" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># The kACE feed: which tenors are posted as pillars, and the ATM bid/offer</t>
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t># The kACE feed: which tenors are posted as pillars, and the ATM bid/offer</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># width at each, in volatility points.  Read by volkit/kace.py.</t>
+      <c r="A2" s="99" t="inlineStr">
+        <is>
+          <t># width at each, in volatility points.  Read by volkit/kace.py.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># The tenors listed for a pair are exactly the pillars posted for it, so a</t>
+      <c r="A4" s="99" t="inlineStr">
+        <is>
+          <t># The tenors listed for a pair are exactly the pillars posted for it, so a</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># pair with no rows here cannot be posted, and a tenor listed here with no</t>
+      <c r="A5" s="99" t="inlineStr">
+        <is>
+          <t># pair with no rows here cannot be posted, and a tenor listed here with no</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># wing marks in the workbook is refused by name.  O/N is the one-day option</t>
+      <c r="A6" s="99" t="inlineStr">
+        <is>
+          <t># wing marks in the workbook is refused by name.  O/N is the one-day option</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># and borrows the shortest quoted tenor's wings.</t>
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t># and borrows the shortest quoted tenor's wings.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># A day between two pillars takes the spread of the earlier one; a day before</t>
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t># A day between two pillars takes the spread of the earlier one; a day before</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># the O/N expiry takes O/N's.  These rows are the USDCNH sheet's column L.</t>
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t># the O/N expiry takes O/N's.  These rows are the USDCNH sheet's column L.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pair</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">tenor</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">spread</t>
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>pair</t>
+        </is>
+      </c>
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>tenor</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr">
+        <is>
+          <t>spread</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O/N</t>
-        </is>
-      </c>
-      <c r="C12">
-        <v>1.0</v>
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>O/N</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1W</t>
-        </is>
-      </c>
-      <c r="C13">
+      <c r="A13" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="C13" s="99" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2W</t>
-        </is>
-      </c>
-      <c r="C14">
+      <c r="A14" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="C14" s="99" t="n">
         <v>0.6</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1M</t>
-        </is>
-      </c>
-      <c r="C15">
+      <c r="A15" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B15" s="99" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="C15" s="99" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2M</t>
-        </is>
-      </c>
-      <c r="C16">
+      <c r="A16" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B16" s="99" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="C16" s="99" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3M</t>
-        </is>
-      </c>
-      <c r="C17">
+      <c r="A17" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B17" s="99" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="C17" s="99" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6M</t>
-        </is>
-      </c>
-      <c r="C18">
+      <c r="A18" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B18" s="99" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="C18" s="99" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9M</t>
-        </is>
-      </c>
-      <c r="C19">
+      <c r="A19" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B19" s="99" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="C19" s="99" t="n">
         <v>0.2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">USDCNH</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1Y</t>
-        </is>
-      </c>
-      <c r="C20">
+      <c r="A20" s="99" t="inlineStr">
+        <is>
+          <t>USDCNH</t>
+        </is>
+      </c>
+      <c r="B20" s="99" t="inlineStr">
+        <is>
+          <t>1Y</t>
+        </is>
+      </c>
+      <c r="C20" s="99" t="n">
         <v>0.2</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="14" customWidth="1"/>
-    <col min="3" max="3" width="10" customWidth="1"/>
+    <col width="12" customWidth="1" style="102" min="1" max="1"/>
+    <col width="14" customWidth="1" style="102" min="2" max="2"/>
+    <col width="10" customWidth="1" style="102" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Holiday dates no rule derives: country, date, remove.</t>
+      <c r="A1" s="99" t="inlineStr">
+        <is>
+          <t># Holiday dates no rule derives: country, date, remove.</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A2" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Lunar-calendar holidays are published annually and cannot be worked out from</t>
+      <c r="A3" s="99" t="inlineStr">
+        <is>
+          <t># Lunar-calendar holidays are published annually and cannot be worked out from</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># rules, so they are listed here. A row with remove = yes takes a date away</t>
+      <c r="A4" s="99" t="inlineStr">
+        <is>
+          <t># rules, so they are listed here. A row with remove = yes takes a date away</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># that the built-in rules would otherwise make a holiday.</t>
+      <c r="A5" s="99" t="inlineStr">
+        <is>
+          <t># that the built-in rules would otherwise make a holiday.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#</t>
+      <c r="A6" s="99" t="inlineStr">
+        <is>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Dates are YYYY-MM-DD. A '#' in the first column makes the whole row a note.</t>
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t># Dates are YYYY-MM-DD. A '#' in the first column makes the whole row a note.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">country</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">date</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">remove</t>
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B8" s="99" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C8" s="99" t="inlineStr">
+        <is>
+          <t>remove</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Chinese New Year 2025</t>
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t># Chinese New Year 2025</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-01-28</t>
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>2025-01-28</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-01-29</t>
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>2025-01-29</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-01-30</t>
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>2025-01-30</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-01-31</t>
+      <c r="A13" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-02-03</t>
+      <c r="A14" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B14" s="99" t="inlineStr">
+        <is>
+          <t>2025-02-03</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2025-02-04</t>
+      <c r="A15" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B15" s="99" t="inlineStr">
+        <is>
+          <t>2025-02-04</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t xml:space="preserve"># Chinese New Year 2026</t>
+      <c r="A16" s="99" t="inlineStr">
+        <is>
+          <t># Chinese New Year 2026</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-16</t>
+      <c r="A17" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B17" s="99" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-17</t>
+      <c r="A18" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B18" s="99" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-18</t>
+      <c r="A19" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B19" s="99" t="inlineStr">
+        <is>
+          <t>2026-02-18</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-19</t>
+      <c r="A20" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B20" s="99" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CN</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2026-02-20</t>
+      <c r="A21" s="99" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="B21" s="99" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 

--- a/files/vol_marks.xlsx
+++ b/files/vol_marks.xlsx
@@ -7332,12 +7332,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="102" min="1" max="1"/>
-    <col width="10" customWidth="1" style="102" min="2" max="2"/>
-    <col width="10" customWidth="1" style="102" min="3" max="3"/>
+    <col width="10" customWidth="1" style="102" min="2" max="4"/>
+    <col width="30" customWidth="1" style="102" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7364,28 +7364,28 @@
     <row r="4">
       <c r="A4" s="99" t="inlineStr">
         <is>
-          <t># The tenors listed for a pair are exactly the pillars posted for it, so a</t>
+          <t># One row per tenor -- those are the pillars posted, so a tab with no rows</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="99" t="inlineStr">
         <is>
-          <t># pair with no rows here cannot be posted, and a tenor listed here with no</t>
+          <t># cannot be posted, and a tenor listed here with no wing marks in the</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="99" t="inlineStr">
         <is>
-          <t># wing marks in the workbook is refused by name.  O/N is the one-day option</t>
+          <t># workbook is refused by name.  O/N is the one-day option and borrows the</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="99" t="inlineStr">
         <is>
-          <t># and borrows the shortest quoted tenor's wings.</t>
+          <t># shortest quoted tenor's wings.</t>
         </is>
       </c>
     </row>
@@ -7399,171 +7399,238 @@
     <row r="9">
       <c r="A9" s="99" t="inlineStr">
         <is>
-          <t># A day between two pillars takes the spread of the earlier one; a day before</t>
+          <t># One column per spreading TIER: 'default', plus whatever else the desk</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="99" t="inlineStr">
         <is>
-          <t># the O/N expiry takes O/N's.  These rows are the USDCNH sheet's column L.</t>
+          <t># names.  A tier is a quoting policy and not a currency -- the pair is</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="99" t="inlineStr">
         <is>
-          <t>pair</t>
-        </is>
-      </c>
-      <c r="B11" s="99" t="inlineStr">
-        <is>
-          <t>tenor</t>
-        </is>
-      </c>
-      <c r="C11" s="99" t="inlineStr">
-        <is>
-          <t>spread</t>
+          <t># chosen on the kACE feed screen beside the tier -- and a cell a tier</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B12" s="99" t="inlineStr">
-        <is>
-          <t>O/N</t>
-        </is>
-      </c>
-      <c r="C12" s="99" t="n">
-        <v>1</v>
+          <t># leaves blank takes 'default' for that tenor.  Tiers are added, edited</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B13" s="99" t="inlineStr">
-        <is>
-          <t>1W</t>
-        </is>
-      </c>
-      <c r="C13" s="99" t="n">
-        <v>0.8</v>
+          <t># and removed in the Config window, and reach this file with the marks.</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B14" s="99" t="inlineStr">
-        <is>
-          <t>2W</t>
-        </is>
-      </c>
-      <c r="C14" s="99" t="n">
-        <v>0.6</v>
+          <t>#</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B15" s="99" t="inlineStr">
-        <is>
-          <t>1M</t>
-        </is>
-      </c>
-      <c r="C15" s="99" t="n">
-        <v>0.4</v>
+          <t># A day between two pillars takes the spread of the earlier one; a day before</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B16" s="99" t="inlineStr">
-        <is>
-          <t>2M</t>
-        </is>
-      </c>
-      <c r="C16" s="99" t="n">
-        <v>0.3</v>
+          <t># the O/N expiry takes O/N's.  The 'default' column is the USDCNH sheet's</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B17" s="99" t="inlineStr">
-        <is>
-          <t>3M</t>
-        </is>
-      </c>
-      <c r="C17" s="99" t="n">
-        <v>0.3</v>
+          <t># column L, which is where this table started.</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
+          <t>tenor</t>
         </is>
       </c>
       <c r="B18" s="99" t="inlineStr">
         <is>
-          <t>6M</t>
-        </is>
-      </c>
-      <c r="C18" s="99" t="n">
-        <v>0.2</v>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C18" s="99" t="inlineStr">
+        <is>
+          <t>wide</t>
+        </is>
+      </c>
+      <c r="D18" s="99" t="inlineStr">
+        <is>
+          <t>thin</t>
+        </is>
+      </c>
+      <c r="E18" s="99" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B19" s="99" t="inlineStr">
-        <is>
-          <t>9M</t>
-        </is>
+          <t>O/N</t>
+        </is>
+      </c>
+      <c r="B19" s="99" t="n">
+        <v>1</v>
       </c>
       <c r="C19" s="99" t="n">
-        <v>0.2</v>
+        <v>1.5</v>
+      </c>
+      <c r="D19" s="99" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="99" t="inlineStr">
         <is>
-          <t>USDCNH</t>
-        </is>
-      </c>
-      <c r="B20" s="99" t="inlineStr">
+          <t>1W</t>
+        </is>
+      </c>
+      <c r="B20" s="99" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C20" s="99" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="D20" s="99" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="99" t="inlineStr">
+        <is>
+          <t>2W</t>
+        </is>
+      </c>
+      <c r="B21" s="99" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C21" s="99" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D21" s="99" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="99" t="inlineStr">
+        <is>
+          <t>1M</t>
+        </is>
+      </c>
+      <c r="B22" s="99" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C22" s="99" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D22" s="99" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="99" t="inlineStr">
+        <is>
+          <t>2M</t>
+        </is>
+      </c>
+      <c r="B23" s="99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C23" s="99" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D23" s="99" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="99" t="inlineStr">
+        <is>
+          <t>3M</t>
+        </is>
+      </c>
+      <c r="B24" s="99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C24" s="99" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D24" s="99" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="99" t="inlineStr">
+        <is>
+          <t>6M</t>
+        </is>
+      </c>
+      <c r="B25" s="99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C25" s="99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D25" s="99" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="99" t="inlineStr">
+        <is>
+          <t>9M</t>
+        </is>
+      </c>
+      <c r="B26" s="99" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C26" s="99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D26" s="99" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="99" t="inlineStr">
         <is>
           <t>1Y</t>
         </is>
       </c>
-      <c r="C20" s="99" t="n">
+      <c r="B27" s="99" t="n">
         <v>0.2</v>
       </c>
+      <c r="C27" s="99" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D27" s="99" t="n">
+        <v>0.15</v>
+      </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
